--- a/04_Figures/F06_prediction/modules/training/ridge/c_data/results.xlsx
+++ b/04_Figures/F06_prediction/modules/training/ridge/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -168,12 +168,6 @@
   </si>
   <si>
     <t xml:space="preserve">ME_red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise</t>
@@ -566,7 +560,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -599,7 +593,7 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
         <v>200</v>
@@ -611,16 +605,16 @@
         <v>-1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.238805970149254</v>
+        <v>0.213930348258706</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.15891642296619</v>
+        <v>-0.193642624859451</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0139788331582956</v>
+        <v>0.167067254755642</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +634,7 @@
         <v>14</v>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -673,7 +667,7 @@
         <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
         <v>200</v>
@@ -685,16 +679,16 @@
         <v>-1</v>
       </c>
       <c r="J5" t="n">
-        <v>0.900497512437811</v>
+        <v>0.587064676616915</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.16033283255451</v>
+        <v>-0.230179012603692</v>
       </c>
       <c r="M5" t="n">
-        <v>0.00386897040447863</v>
+        <v>0.206821586734155</v>
       </c>
     </row>
     <row r="6">
@@ -714,16 +708,16 @@
         <v>14</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.472854194083004</v>
       </c>
       <c r="I6" t="n">
-        <v>-1</v>
+        <v>-0.986813186813187</v>
       </c>
       <c r="J6"/>
       <c r="K6"/>
@@ -747,28 +741,28 @@
         <v>14</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
         <v>200</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.472854194083004</v>
       </c>
       <c r="I7" t="n">
-        <v>-1</v>
+        <v>-0.986813186813187</v>
       </c>
       <c r="J7" t="n">
-        <v>0.472636815920398</v>
+        <v>0.920398009950249</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0.313432835820896</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.159520253777073</v>
+        <v>-0.22399775026837</v>
       </c>
       <c r="M7" t="n">
-        <v>0.00631142010915652</v>
+        <v>0.204281752905212</v>
       </c>
     </row>
     <row r="8">
@@ -788,7 +782,7 @@
         <v>14</v>
       </c>
       <c r="F8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -821,7 +815,7 @@
         <v>14</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
         <v>200</v>
@@ -833,16 +827,16 @@
         <v>-1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.577114427860697</v>
+        <v>0.442786069651741</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.159907421507485</v>
+        <v>-0.206808567016426</v>
       </c>
       <c r="M9" t="n">
-        <v>0.00195700411208143</v>
+        <v>0.206153358111677</v>
       </c>
     </row>
     <row r="10">
@@ -862,16 +856,16 @@
         <v>14</v>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.699753337637119</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.996690559042565</v>
+        <v>-0.987850731467909</v>
       </c>
       <c r="J10"/>
       <c r="K10"/>
@@ -895,28 +889,28 @@
         <v>14</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
         <v>200</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.699753337637119</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.996690559042565</v>
+        <v>-0.987850731467909</v>
       </c>
       <c r="J11" t="n">
-        <v>0.81592039800995</v>
+        <v>0.980099502487562</v>
       </c>
       <c r="K11" t="n">
-        <v>0.502487562189055</v>
+        <v>0.393034825870647</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.159577766047622</v>
+        <v>-0.216095674753085</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0171474824703385</v>
+        <v>0.256695464224787</v>
       </c>
     </row>
     <row r="12">
@@ -936,16 +930,16 @@
         <v>13</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.239096732581834</v>
       </c>
       <c r="I12" t="n">
-        <v>-1</v>
+        <v>-0.553721109373828</v>
       </c>
       <c r="J12"/>
       <c r="K12"/>
@@ -969,28 +963,28 @@
         <v>13</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
         <v>200</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.239096732581834</v>
       </c>
       <c r="I13" t="n">
-        <v>-1</v>
+        <v>-0.553721109373828</v>
       </c>
       <c r="J13" t="n">
-        <v>0.407960199004975</v>
+        <v>0.756218905472637</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0.104477611940299</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.172991688455168</v>
+        <v>-0.236043039987825</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0102754876664405</v>
+        <v>0.197453540015227</v>
       </c>
     </row>
   </sheetData>
@@ -1045,7 +1039,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.229508803803176</v>
       </c>
     </row>
     <row r="5">
@@ -1078,7 +1072,7 @@
         <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.125966637284927</v>
+        <v>0.212959223953838</v>
       </c>
     </row>
     <row r="8">
@@ -1089,7 +1083,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.247913157696572</v>
       </c>
     </row>
     <row r="9">
@@ -1111,7 +1105,7 @@
         <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.20142970455123</v>
       </c>
     </row>
     <row r="11">
@@ -1122,7 +1116,7 @@
         <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.224522277832352</v>
       </c>
     </row>
     <row r="12">
@@ -1133,7 +1127,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.353779535827448</v>
       </c>
     </row>
     <row r="13">
@@ -1144,7 +1138,7 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.159007740474607</v>
+        <v>-0.0128106235575576</v>
       </c>
     </row>
     <row r="14">
@@ -1177,7 +1171,7 @@
         <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.203728030426336</v>
       </c>
     </row>
     <row r="17">
@@ -1254,7 +1248,7 @@
         <v>16</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.228444427643573</v>
       </c>
     </row>
     <row r="24">
@@ -1287,7 +1281,7 @@
         <v>16</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.432944097136105</v>
       </c>
     </row>
     <row r="27">
@@ -1298,7 +1292,7 @@
         <v>16</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.217739964937987</v>
       </c>
     </row>
     <row r="28">
@@ -1309,7 +1303,7 @@
         <v>16</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.425799617735444</v>
       </c>
     </row>
     <row r="29">
@@ -1364,7 +1358,7 @@
         <v>16</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.215983621354486</v>
       </c>
     </row>
     <row r="34">
@@ -1375,7 +1369,7 @@
         <v>16</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.160213353105674</v>
+        <v>0.075766050810089</v>
       </c>
     </row>
     <row r="35">
@@ -1408,7 +1402,7 @@
         <v>16</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.179781663997247</v>
       </c>
     </row>
     <row r="38">
@@ -1419,7 +1413,7 @@
         <v>16</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.225903774257976</v>
       </c>
     </row>
     <row r="39">
@@ -1430,7 +1424,7 @@
         <v>16</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.160443554435486</v>
+        <v>-0.204164245343307</v>
       </c>
     </row>
     <row r="40">
@@ -1441,7 +1435,7 @@
         <v>16</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.687298543767883</v>
       </c>
     </row>
     <row r="41">
@@ -1452,7 +1446,7 @@
         <v>16</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.162080136169021</v>
+        <v>-0.321123082577313</v>
       </c>
     </row>
     <row r="42">
@@ -1485,7 +1479,7 @@
         <v>16</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.187530129203168</v>
       </c>
     </row>
     <row r="45">
@@ -1507,7 +1501,7 @@
         <v>16</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.213833230710461</v>
+        <v>-0.335662070659182</v>
       </c>
     </row>
     <row r="47">
@@ -1540,7 +1534,7 @@
         <v>16</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.160451095624118</v>
+        <v>-0.16655780475482</v>
       </c>
     </row>
     <row r="50">
@@ -1562,7 +1556,7 @@
         <v>16</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.159763313609468</v>
+        <v>0.0927381546174252</v>
       </c>
     </row>
     <row r="52">
@@ -1573,7 +1567,7 @@
         <v>16</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.338086749907712</v>
       </c>
     </row>
     <row r="53">
@@ -1584,7 +1578,7 @@
         <v>16</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.730810991658151</v>
       </c>
     </row>
     <row r="54">
@@ -1639,7 +1633,7 @@
         <v>16</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.285299511090914</v>
       </c>
     </row>
     <row r="59">
@@ -1650,7 +1644,7 @@
         <v>16</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.170439177224845</v>
+        <v>-0.303632662715264</v>
       </c>
     </row>
     <row r="60">
@@ -1672,7 +1666,7 @@
         <v>16</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.175724929729658</v>
+        <v>-0.123538531308734</v>
       </c>
     </row>
     <row r="62">
@@ -1683,7 +1677,7 @@
         <v>16</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.339815153756975</v>
       </c>
     </row>
     <row r="63">
@@ -1694,7 +1688,7 @@
         <v>16</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.180064382199257</v>
       </c>
     </row>
     <row r="64">
@@ -1705,7 +1699,7 @@
         <v>16</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.180267669744242</v>
+        <v>-0.402791114446741</v>
       </c>
     </row>
     <row r="65">
@@ -1716,7 +1710,7 @@
         <v>16</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.332225454067946</v>
       </c>
     </row>
     <row r="66">
@@ -1727,7 +1721,7 @@
         <v>16</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.55811381049068</v>
       </c>
     </row>
     <row r="67">
@@ -1749,7 +1743,7 @@
         <v>16</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.358335501388649</v>
       </c>
     </row>
     <row r="69">
@@ -1892,7 +1886,7 @@
         <v>16</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.368291439661994</v>
       </c>
     </row>
     <row r="82">
@@ -1903,7 +1897,7 @@
         <v>16</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.18308269021516</v>
       </c>
     </row>
     <row r="83">
@@ -1969,7 +1963,7 @@
         <v>16</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.190854494995054</v>
       </c>
     </row>
     <row r="89">
@@ -1980,7 +1974,7 @@
         <v>16</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.160649368927769</v>
       </c>
     </row>
     <row r="90">
@@ -1991,7 +1985,7 @@
         <v>16</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.19502363675795</v>
       </c>
     </row>
     <row r="91">
@@ -2035,7 +2029,7 @@
         <v>16</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.119669231769141</v>
       </c>
     </row>
     <row r="95">
@@ -2057,7 +2051,7 @@
         <v>16</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.56713439896578</v>
       </c>
     </row>
     <row r="97">
@@ -2090,7 +2084,7 @@
         <v>16</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.165248989773074</v>
+        <v>-0.200426866887341</v>
       </c>
     </row>
     <row r="100">
@@ -2167,7 +2161,7 @@
         <v>16</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.319689365099051</v>
       </c>
     </row>
     <row r="107">
@@ -2178,7 +2172,7 @@
         <v>16</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.297825149289978</v>
       </c>
     </row>
     <row r="108">
@@ -2200,7 +2194,7 @@
         <v>16</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.161120772654072</v>
       </c>
     </row>
     <row r="110">
@@ -2211,7 +2205,7 @@
         <v>16</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.167122816585518</v>
       </c>
     </row>
     <row r="111">
@@ -2222,7 +2216,7 @@
         <v>16</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.197364625428792</v>
       </c>
     </row>
     <row r="112">
@@ -2255,7 +2249,7 @@
         <v>16</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.178837036315235</v>
       </c>
     </row>
     <row r="115">
@@ -2266,7 +2260,7 @@
         <v>16</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.270014225822065</v>
       </c>
     </row>
     <row r="116">
@@ -2288,7 +2282,7 @@
         <v>16</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.17319693914776</v>
+        <v>-0.257884648445696</v>
       </c>
     </row>
     <row r="118">
@@ -2321,7 +2315,7 @@
         <v>16</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.173470240166341</v>
       </c>
     </row>
     <row r="121">
@@ -2354,7 +2348,7 @@
         <v>16</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.166069203470861</v>
       </c>
     </row>
     <row r="124">
@@ -2365,7 +2359,7 @@
         <v>16</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.16648981728009</v>
+        <v>-0.22929868820004</v>
       </c>
     </row>
     <row r="125">
@@ -2431,7 +2425,7 @@
         <v>16</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.0686849324396033</v>
       </c>
     </row>
     <row r="131">
@@ -2442,7 +2436,7 @@
         <v>16</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.175606059516892</v>
       </c>
     </row>
     <row r="132">
@@ -2475,7 +2469,7 @@
         <v>16</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.224617212581103</v>
       </c>
     </row>
     <row r="135">
@@ -2508,7 +2502,7 @@
         <v>16</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.162676213489837</v>
+        <v>-0.147717092103524</v>
       </c>
     </row>
     <row r="138">
@@ -2530,7 +2524,7 @@
         <v>16</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.222448862330739</v>
       </c>
     </row>
     <row r="140">
@@ -2541,7 +2535,7 @@
         <v>16</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.160728593650018</v>
       </c>
     </row>
     <row r="141">
@@ -2552,7 +2546,7 @@
         <v>16</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.130462750045943</v>
+        <v>-0.0295922059377394</v>
       </c>
     </row>
     <row r="142">
@@ -2607,7 +2601,7 @@
         <v>16</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.156904845276899</v>
       </c>
     </row>
     <row r="147">
@@ -2629,7 +2623,7 @@
         <v>16</v>
       </c>
       <c r="C148" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.163395709125837</v>
       </c>
     </row>
     <row r="149">
@@ -2640,7 +2634,7 @@
         <v>16</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.16005710973361</v>
+        <v>-0.312282780672512</v>
       </c>
     </row>
     <row r="150">
@@ -2651,7 +2645,7 @@
         <v>16</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.329465790107647</v>
       </c>
     </row>
     <row r="151">
@@ -2673,7 +2667,7 @@
         <v>16</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.151677137303957</v>
+        <v>-0.540210896925693</v>
       </c>
     </row>
     <row r="153">
@@ -2684,7 +2678,7 @@
         <v>16</v>
       </c>
       <c r="C153" t="n">
-        <v>-0.161445399919724</v>
+        <v>-0.167148237455301</v>
       </c>
     </row>
     <row r="154">
@@ -2706,7 +2700,7 @@
         <v>16</v>
       </c>
       <c r="C155" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.370051671821662</v>
       </c>
     </row>
     <row r="156">
@@ -2717,7 +2711,7 @@
         <v>16</v>
       </c>
       <c r="C156" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.744691509667154</v>
       </c>
     </row>
     <row r="157">
@@ -2728,7 +2722,7 @@
         <v>16</v>
       </c>
       <c r="C157" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.746759455734333</v>
       </c>
     </row>
     <row r="158">
@@ -2739,7 +2733,7 @@
         <v>16</v>
       </c>
       <c r="C158" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.375148811267136</v>
       </c>
     </row>
     <row r="159">
@@ -2761,7 +2755,7 @@
         <v>16</v>
       </c>
       <c r="C160" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.229797185293113</v>
       </c>
     </row>
     <row r="161">
@@ -2816,7 +2810,7 @@
         <v>16</v>
       </c>
       <c r="C165" t="n">
-        <v>-0.138035810155194</v>
+        <v>-0.0511817197908426</v>
       </c>
     </row>
     <row r="166">
@@ -2827,7 +2821,7 @@
         <v>16</v>
       </c>
       <c r="C166" t="n">
-        <v>-0.159763313609468</v>
+        <v>0.393030430627571</v>
       </c>
     </row>
     <row r="167">
@@ -2849,7 +2843,7 @@
         <v>16</v>
       </c>
       <c r="C168" t="n">
-        <v>-0.16797604623632</v>
+        <v>-0.170641856973881</v>
       </c>
     </row>
     <row r="169">
@@ -2860,7 +2854,7 @@
         <v>16</v>
       </c>
       <c r="C169" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.248574785538624</v>
       </c>
     </row>
     <row r="170">
@@ -2893,7 +2887,7 @@
         <v>16</v>
       </c>
       <c r="C172" t="n">
-        <v>-0.166935594589898</v>
+        <v>-0.222218728445539</v>
       </c>
     </row>
     <row r="173">
@@ -2904,7 +2898,7 @@
         <v>16</v>
       </c>
       <c r="C173" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.389258648708634</v>
       </c>
     </row>
     <row r="174">
@@ -2915,7 +2909,7 @@
         <v>16</v>
       </c>
       <c r="C174" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.202140480683973</v>
       </c>
     </row>
     <row r="175">
@@ -2926,7 +2920,7 @@
         <v>16</v>
       </c>
       <c r="C175" t="n">
-        <v>-0.165060146558105</v>
+        <v>-0.0298858172038865</v>
       </c>
     </row>
     <row r="176">
@@ -2937,7 +2931,7 @@
         <v>16</v>
       </c>
       <c r="C176" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.184431885579826</v>
       </c>
     </row>
     <row r="177">
@@ -2948,7 +2942,7 @@
         <v>16</v>
       </c>
       <c r="C177" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.177808281363468</v>
       </c>
     </row>
     <row r="178">
@@ -2981,7 +2975,7 @@
         <v>16</v>
       </c>
       <c r="C180" t="n">
-        <v>-0.159174150507248</v>
+        <v>-0.179144410426889</v>
       </c>
     </row>
     <row r="181">
@@ -2992,7 +2986,7 @@
         <v>16</v>
       </c>
       <c r="C181" t="n">
-        <v>-0.215423203191407</v>
+        <v>-0.36538387962037</v>
       </c>
     </row>
     <row r="182">
@@ -3014,7 +3008,7 @@
         <v>16</v>
       </c>
       <c r="C183" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.197275928403263</v>
       </c>
     </row>
     <row r="184">
@@ -3025,7 +3019,7 @@
         <v>16</v>
       </c>
       <c r="C184" t="n">
-        <v>-0.182679785138522</v>
+        <v>-0.227055562112566</v>
       </c>
     </row>
     <row r="185">
@@ -3036,7 +3030,7 @@
         <v>16</v>
       </c>
       <c r="C185" t="n">
-        <v>-0.0240306892322353</v>
+        <v>0.505053712722022</v>
       </c>
     </row>
     <row r="186">
@@ -3047,7 +3041,7 @@
         <v>16</v>
       </c>
       <c r="C186" t="n">
-        <v>-0.0913792344188342</v>
+        <v>0.729295331537263</v>
       </c>
     </row>
     <row r="187">
@@ -3069,7 +3063,7 @@
         <v>16</v>
       </c>
       <c r="C188" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.126973146317147</v>
       </c>
     </row>
     <row r="189">
@@ -3080,7 +3074,7 @@
         <v>16</v>
       </c>
       <c r="C189" t="n">
-        <v>-0.107307702965041</v>
+        <v>0.203295655127643</v>
       </c>
     </row>
     <row r="190">
@@ -3091,7 +3085,7 @@
         <v>16</v>
       </c>
       <c r="C190" t="n">
-        <v>-0.106073721829166</v>
+        <v>-0.0922165703807081</v>
       </c>
     </row>
     <row r="191">
@@ -3113,7 +3107,7 @@
         <v>16</v>
       </c>
       <c r="C192" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.335335287647958</v>
       </c>
     </row>
     <row r="193">
@@ -3157,7 +3151,7 @@
         <v>16</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.1517397072259</v>
       </c>
     </row>
     <row r="197">
@@ -3168,7 +3162,7 @@
         <v>16</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.257801762016997</v>
       </c>
     </row>
     <row r="198">
@@ -3179,7 +3173,7 @@
         <v>16</v>
       </c>
       <c r="C198" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.365882267846839</v>
       </c>
     </row>
     <row r="199">
@@ -3201,7 +3195,7 @@
         <v>16</v>
       </c>
       <c r="C200" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.366145084345624</v>
       </c>
     </row>
     <row r="201">
@@ -3223,7 +3217,7 @@
         <v>16</v>
       </c>
       <c r="C202" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.314055421798416</v>
       </c>
     </row>
     <row r="203">
@@ -3245,7 +3239,7 @@
         <v>16</v>
       </c>
       <c r="C204" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.246163503567078</v>
       </c>
     </row>
     <row r="205">
@@ -3267,7 +3261,7 @@
         <v>16</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.177986244882575</v>
       </c>
     </row>
     <row r="207">
@@ -3278,7 +3272,7 @@
         <v>16</v>
       </c>
       <c r="C207" t="n">
-        <v>-0.163823025043851</v>
+        <v>-0.102155797361915</v>
       </c>
     </row>
     <row r="208">
@@ -3333,7 +3327,7 @@
         <v>16</v>
       </c>
       <c r="C212" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.536455461071391</v>
       </c>
     </row>
     <row r="213">
@@ -3344,7 +3338,7 @@
         <v>16</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.159763313609467</v>
+        <v>0.110154848697996</v>
       </c>
     </row>
     <row r="214">
@@ -3366,7 +3360,7 @@
         <v>16</v>
       </c>
       <c r="C215" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.18079880830582</v>
       </c>
     </row>
     <row r="216">
@@ -3377,7 +3371,7 @@
         <v>16</v>
       </c>
       <c r="C216" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.214107139630209</v>
       </c>
     </row>
     <row r="217">
@@ -3410,7 +3404,7 @@
         <v>16</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.499063240983521</v>
       </c>
     </row>
     <row r="220">
@@ -3443,7 +3437,7 @@
         <v>16</v>
       </c>
       <c r="C222" t="n">
-        <v>-0.173135469649412</v>
+        <v>-1.06103688223301</v>
       </c>
     </row>
     <row r="223">
@@ -3454,7 +3448,7 @@
         <v>16</v>
       </c>
       <c r="C223" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.191524640418346</v>
       </c>
     </row>
     <row r="224">
@@ -3487,7 +3481,7 @@
         <v>16</v>
       </c>
       <c r="C226" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.560908800989527</v>
       </c>
     </row>
     <row r="227">
@@ -3520,7 +3514,7 @@
         <v>16</v>
       </c>
       <c r="C229" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.82401118428515</v>
       </c>
     </row>
     <row r="230">
@@ -3564,7 +3558,7 @@
         <v>16</v>
       </c>
       <c r="C233" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.24398071107758</v>
       </c>
     </row>
     <row r="234">
@@ -3575,7 +3569,7 @@
         <v>16</v>
       </c>
       <c r="C234" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.228968239185483</v>
       </c>
     </row>
     <row r="235">
@@ -3597,7 +3591,7 @@
         <v>16</v>
       </c>
       <c r="C236" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.504173497424451</v>
       </c>
     </row>
     <row r="237">
@@ -3652,7 +3646,7 @@
         <v>16</v>
       </c>
       <c r="C241" t="n">
-        <v>-0.178489668538434</v>
+        <v>-0.227107479409403</v>
       </c>
     </row>
     <row r="242">
@@ -3685,7 +3679,7 @@
         <v>16</v>
       </c>
       <c r="C244" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.228674267559702</v>
       </c>
     </row>
     <row r="245">
@@ -3696,7 +3690,7 @@
         <v>16</v>
       </c>
       <c r="C245" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.278881707180818</v>
       </c>
     </row>
     <row r="246">
@@ -3707,7 +3701,7 @@
         <v>16</v>
       </c>
       <c r="C246" t="n">
-        <v>-0.171055342281679</v>
+        <v>-0.204661199476623</v>
       </c>
     </row>
     <row r="247">
@@ -3718,7 +3712,7 @@
         <v>16</v>
       </c>
       <c r="C247" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.497577381092201</v>
       </c>
     </row>
     <row r="248">
@@ -3740,7 +3734,7 @@
         <v>16</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.783009740579179</v>
       </c>
     </row>
     <row r="250">
@@ -3762,7 +3756,7 @@
         <v>16</v>
       </c>
       <c r="C251" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.363608307694684</v>
       </c>
     </row>
     <row r="252">
@@ -3839,7 +3833,7 @@
         <v>16</v>
       </c>
       <c r="C258" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.207122088378464</v>
       </c>
     </row>
     <row r="259">
@@ -3872,7 +3866,7 @@
         <v>16</v>
       </c>
       <c r="C261" t="n">
-        <v>-0.156039478299042</v>
+        <v>-0.16282726621983</v>
       </c>
     </row>
     <row r="262">
@@ -3905,7 +3899,7 @@
         <v>16</v>
       </c>
       <c r="C264" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.829295583429722</v>
       </c>
     </row>
     <row r="265">
@@ -3916,7 +3910,7 @@
         <v>16</v>
       </c>
       <c r="C265" t="n">
-        <v>-0.161663460949306</v>
+        <v>-0.478181889567022</v>
       </c>
     </row>
     <row r="266">
@@ -3927,7 +3921,7 @@
         <v>16</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.377171408015422</v>
       </c>
     </row>
     <row r="267">
@@ -3938,7 +3932,7 @@
         <v>16</v>
       </c>
       <c r="C267" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.14596153055271</v>
       </c>
     </row>
     <row r="268">
@@ -3949,7 +3943,7 @@
         <v>16</v>
       </c>
       <c r="C268" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.443622132515104</v>
       </c>
     </row>
     <row r="269">
@@ -3993,7 +3987,7 @@
         <v>16</v>
       </c>
       <c r="C272" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.976409525379704</v>
       </c>
     </row>
     <row r="273">
@@ -4059,7 +4053,7 @@
         <v>16</v>
       </c>
       <c r="C278" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.169705630456413</v>
       </c>
     </row>
     <row r="279">
@@ -4092,7 +4086,7 @@
         <v>16</v>
       </c>
       <c r="C281" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.33760745938026</v>
       </c>
     </row>
     <row r="282">
@@ -4125,7 +4119,7 @@
         <v>16</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.270446382227577</v>
       </c>
     </row>
     <row r="285">
@@ -4136,7 +4130,7 @@
         <v>16</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.510156485352851</v>
       </c>
     </row>
     <row r="286">
@@ -4147,7 +4141,7 @@
         <v>16</v>
       </c>
       <c r="C286" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.182908211141403</v>
       </c>
     </row>
     <row r="287">
@@ -4180,7 +4174,7 @@
         <v>16</v>
       </c>
       <c r="C289" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.181021107633848</v>
       </c>
     </row>
     <row r="290">
@@ -4191,7 +4185,7 @@
         <v>16</v>
       </c>
       <c r="C290" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.192514284900859</v>
       </c>
     </row>
     <row r="291">
@@ -4235,7 +4229,7 @@
         <v>16</v>
       </c>
       <c r="C294" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.286640044854566</v>
       </c>
     </row>
     <row r="295">
@@ -4246,7 +4240,7 @@
         <v>16</v>
       </c>
       <c r="C295" t="n">
-        <v>-0.163643001977232</v>
+        <v>-0.167038886657537</v>
       </c>
     </row>
     <row r="296">
@@ -4257,7 +4251,7 @@
         <v>16</v>
       </c>
       <c r="C296" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.805174407905417</v>
       </c>
     </row>
     <row r="297">
@@ -4268,7 +4262,7 @@
         <v>16</v>
       </c>
       <c r="C297" t="n">
-        <v>-0.176505836190979</v>
+        <v>-0.222901705019624</v>
       </c>
     </row>
     <row r="298">
@@ -4279,7 +4273,7 @@
         <v>16</v>
       </c>
       <c r="C298" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.395085488681517</v>
       </c>
     </row>
     <row r="299">
@@ -4334,7 +4328,7 @@
         <v>16</v>
       </c>
       <c r="C303" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.307098029033022</v>
       </c>
     </row>
     <row r="304">
@@ -4378,7 +4372,7 @@
         <v>16</v>
       </c>
       <c r="C307" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.259018840300191</v>
       </c>
     </row>
     <row r="308">
@@ -4389,7 +4383,7 @@
         <v>16</v>
       </c>
       <c r="C308" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.211906952091453</v>
       </c>
     </row>
     <row r="309">
@@ -4400,7 +4394,7 @@
         <v>16</v>
       </c>
       <c r="C309" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.310347447156296</v>
       </c>
     </row>
     <row r="310">
@@ -4411,7 +4405,7 @@
         <v>16</v>
       </c>
       <c r="C310" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.162308863388019</v>
       </c>
     </row>
     <row r="311">
@@ -4422,7 +4416,7 @@
         <v>16</v>
       </c>
       <c r="C311" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.348500617689103</v>
       </c>
     </row>
     <row r="312">
@@ -4433,7 +4427,7 @@
         <v>16</v>
       </c>
       <c r="C312" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.247936801673202</v>
       </c>
     </row>
     <row r="313">
@@ -4444,7 +4438,7 @@
         <v>16</v>
       </c>
       <c r="C313" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.174185185188169</v>
       </c>
     </row>
     <row r="314">
@@ -4455,7 +4449,7 @@
         <v>16</v>
       </c>
       <c r="C314" t="n">
-        <v>-0.176830477131201</v>
+        <v>-0.185463810657832</v>
       </c>
     </row>
     <row r="315">
@@ -4488,7 +4482,7 @@
         <v>16</v>
       </c>
       <c r="C317" t="n">
-        <v>-0.166061811776052</v>
+        <v>-0.290139249209862</v>
       </c>
     </row>
     <row r="318">
@@ -4521,7 +4515,7 @@
         <v>16</v>
       </c>
       <c r="C320" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.33359073873003</v>
       </c>
     </row>
     <row r="321">
@@ -4532,7 +4526,7 @@
         <v>16</v>
       </c>
       <c r="C321" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.259309655502085</v>
       </c>
     </row>
     <row r="322">
@@ -4543,7 +4537,7 @@
         <v>16</v>
       </c>
       <c r="C322" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.220754973053852</v>
       </c>
     </row>
     <row r="323">
@@ -4554,7 +4548,7 @@
         <v>16</v>
       </c>
       <c r="C323" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.293437599682394</v>
       </c>
     </row>
     <row r="324">
@@ -4565,7 +4559,7 @@
         <v>16</v>
       </c>
       <c r="C324" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.206186523145178</v>
       </c>
     </row>
     <row r="325">
@@ -4576,7 +4570,7 @@
         <v>16</v>
       </c>
       <c r="C325" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.193092999707611</v>
       </c>
     </row>
     <row r="326">
@@ -4609,7 +4603,7 @@
         <v>16</v>
       </c>
       <c r="C328" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.32137986027231</v>
       </c>
     </row>
     <row r="329">
@@ -4631,7 +4625,7 @@
         <v>16</v>
       </c>
       <c r="C330" t="n">
-        <v>-0.159763313609467</v>
+        <v>0.370134944461574</v>
       </c>
     </row>
     <row r="331">
@@ -4653,7 +4647,7 @@
         <v>16</v>
       </c>
       <c r="C332" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.18014032048545</v>
       </c>
     </row>
     <row r="333">
@@ -4697,7 +4691,7 @@
         <v>16</v>
       </c>
       <c r="C336" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.862364228043506</v>
       </c>
     </row>
     <row r="337">
@@ -4708,7 +4702,7 @@
         <v>16</v>
       </c>
       <c r="C337" t="n">
-        <v>-0.162711287348508</v>
+        <v>0.288539418374096</v>
       </c>
     </row>
     <row r="338">
@@ -4763,7 +4757,7 @@
         <v>16</v>
       </c>
       <c r="C342" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.167755239979743</v>
       </c>
     </row>
     <row r="343">
@@ -4774,7 +4768,7 @@
         <v>16</v>
       </c>
       <c r="C343" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.212533813601211</v>
       </c>
     </row>
     <row r="344">
@@ -4807,7 +4801,7 @@
         <v>16</v>
       </c>
       <c r="C346" t="n">
-        <v>-0.147750863240032</v>
+        <v>-0.113065196062224</v>
       </c>
     </row>
     <row r="347">
@@ -4818,7 +4812,7 @@
         <v>16</v>
       </c>
       <c r="C347" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.228839427502372</v>
       </c>
     </row>
     <row r="348">
@@ -4829,7 +4823,7 @@
         <v>16</v>
       </c>
       <c r="C348" t="n">
-        <v>-0.159763313609468</v>
+        <v>0.00294089110415163</v>
       </c>
     </row>
     <row r="349">
@@ -4840,7 +4834,7 @@
         <v>16</v>
       </c>
       <c r="C349" t="n">
-        <v>-0.161741639546872</v>
+        <v>-0.137708765788914</v>
       </c>
     </row>
     <row r="350">
@@ -4851,7 +4845,7 @@
         <v>16</v>
       </c>
       <c r="C350" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.360273128492275</v>
       </c>
     </row>
     <row r="351">
@@ -4862,7 +4856,7 @@
         <v>16</v>
       </c>
       <c r="C351" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.24504905783777</v>
       </c>
     </row>
     <row r="352">
@@ -4873,7 +4867,7 @@
         <v>16</v>
       </c>
       <c r="C352" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.66178456122341</v>
       </c>
     </row>
     <row r="353">
@@ -4884,7 +4878,7 @@
         <v>16</v>
       </c>
       <c r="C353" t="n">
-        <v>-0.159763313609467</v>
+        <v>0.276135325198262</v>
       </c>
     </row>
     <row r="354">
@@ -4906,7 +4900,7 @@
         <v>16</v>
       </c>
       <c r="C355" t="n">
-        <v>-0.160687123308811</v>
+        <v>-0.325762039246911</v>
       </c>
     </row>
     <row r="356">
@@ -4917,7 +4911,7 @@
         <v>16</v>
       </c>
       <c r="C356" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.948176234467273</v>
       </c>
     </row>
     <row r="357">
@@ -4928,7 +4922,7 @@
         <v>16</v>
       </c>
       <c r="C357" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.723051956420719</v>
       </c>
     </row>
     <row r="358">
@@ -4939,7 +4933,7 @@
         <v>16</v>
       </c>
       <c r="C358" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.263084934244898</v>
       </c>
     </row>
     <row r="359">
@@ -4972,7 +4966,7 @@
         <v>16</v>
       </c>
       <c r="C361" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.253350568406772</v>
       </c>
     </row>
     <row r="362">
@@ -5016,7 +5010,7 @@
         <v>16</v>
       </c>
       <c r="C365" t="n">
-        <v>-0.160290495627881</v>
+        <v>-0.0996047972914758</v>
       </c>
     </row>
     <row r="366">
@@ -5027,7 +5021,7 @@
         <v>16</v>
       </c>
       <c r="C366" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.04203913724053</v>
       </c>
     </row>
     <row r="367">
@@ -5093,7 +5087,7 @@
         <v>16</v>
       </c>
       <c r="C372" t="n">
-        <v>-0.160697959069593</v>
+        <v>-0.243054783334041</v>
       </c>
     </row>
     <row r="373">
@@ -5104,7 +5098,7 @@
         <v>16</v>
       </c>
       <c r="C373" t="n">
-        <v>-0.177373223306546</v>
+        <v>-0.227297264474519</v>
       </c>
     </row>
     <row r="374">
@@ -5126,7 +5120,7 @@
         <v>16</v>
       </c>
       <c r="C375" t="n">
-        <v>-0.134209658444549</v>
+        <v>0.444381901972657</v>
       </c>
     </row>
     <row r="376">
@@ -5137,7 +5131,7 @@
         <v>16</v>
       </c>
       <c r="C376" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.169336654060534</v>
       </c>
     </row>
     <row r="377">
@@ -5170,7 +5164,7 @@
         <v>16</v>
       </c>
       <c r="C379" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.171942701632051</v>
       </c>
     </row>
     <row r="380">
@@ -5192,7 +5186,7 @@
         <v>16</v>
       </c>
       <c r="C381" t="n">
-        <v>-0.182194988611801</v>
+        <v>-0.399257885231742</v>
       </c>
     </row>
     <row r="382">
@@ -5203,7 +5197,7 @@
         <v>16</v>
       </c>
       <c r="C382" t="n">
-        <v>-0.168817388885533</v>
+        <v>-0.541493455740013</v>
       </c>
     </row>
     <row r="383">
@@ -5236,7 +5230,7 @@
         <v>16</v>
       </c>
       <c r="C385" t="n">
-        <v>-0.161003548926707</v>
+        <v>-0.121961017110926</v>
       </c>
     </row>
     <row r="386">
@@ -5247,7 +5241,7 @@
         <v>16</v>
       </c>
       <c r="C386" t="n">
-        <v>-0.163970940262757</v>
+        <v>-0.094426901193273</v>
       </c>
     </row>
     <row r="387">
@@ -5269,7 +5263,7 @@
         <v>16</v>
       </c>
       <c r="C388" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.144280927504683</v>
       </c>
     </row>
     <row r="389">
@@ -5280,7 +5274,7 @@
         <v>16</v>
       </c>
       <c r="C389" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.00277975129986552</v>
       </c>
     </row>
     <row r="390">
@@ -5291,7 +5285,7 @@
         <v>16</v>
       </c>
       <c r="C390" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.170289916341388</v>
       </c>
     </row>
     <row r="391">
@@ -5302,7 +5296,7 @@
         <v>16</v>
       </c>
       <c r="C391" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.323482722736943</v>
       </c>
     </row>
     <row r="392">
@@ -5313,7 +5307,7 @@
         <v>16</v>
       </c>
       <c r="C392" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.280097298896221</v>
       </c>
     </row>
     <row r="393">
@@ -5346,7 +5340,7 @@
         <v>16</v>
       </c>
       <c r="C395" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.247049581341163</v>
       </c>
     </row>
     <row r="396">
@@ -5379,7 +5373,7 @@
         <v>16</v>
       </c>
       <c r="C398" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.975774960581729</v>
       </c>
     </row>
     <row r="399">
@@ -5423,7 +5417,7 @@
         <v>16</v>
       </c>
       <c r="C402" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.404290862413046</v>
       </c>
     </row>
     <row r="403">
@@ -5445,7 +5439,7 @@
         <v>16</v>
       </c>
       <c r="C404" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.304568087749855</v>
       </c>
     </row>
     <row r="405">
@@ -5467,7 +5461,7 @@
         <v>16</v>
       </c>
       <c r="C406" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.19476088909688</v>
       </c>
     </row>
     <row r="407">
@@ -5478,7 +5472,7 @@
         <v>16</v>
       </c>
       <c r="C407" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.0426126679401604</v>
       </c>
     </row>
     <row r="408">
@@ -5533,7 +5527,7 @@
         <v>16</v>
       </c>
       <c r="C412" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.290071858804288</v>
       </c>
     </row>
     <row r="413">
@@ -5544,7 +5538,7 @@
         <v>16</v>
       </c>
       <c r="C413" t="n">
-        <v>-0.159763313609468</v>
+        <v>0.0513954980516517</v>
       </c>
     </row>
     <row r="414">
@@ -5566,7 +5560,7 @@
         <v>16</v>
       </c>
       <c r="C415" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.205568326521508</v>
       </c>
     </row>
     <row r="416">
@@ -5577,7 +5571,7 @@
         <v>16</v>
       </c>
       <c r="C416" t="n">
-        <v>-0.17677274285</v>
+        <v>-0.229152839876125</v>
       </c>
     </row>
     <row r="417">
@@ -5654,7 +5648,7 @@
         <v>16</v>
       </c>
       <c r="C423" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.487972436901537</v>
       </c>
     </row>
     <row r="424">
@@ -5687,7 +5681,7 @@
         <v>16</v>
       </c>
       <c r="C426" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.65442334968211</v>
       </c>
     </row>
     <row r="427">
@@ -5775,7 +5769,7 @@
         <v>16</v>
       </c>
       <c r="C434" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.175540897328109</v>
       </c>
     </row>
     <row r="435">
@@ -5786,7 +5780,7 @@
         <v>16</v>
       </c>
       <c r="C435" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.188794333285177</v>
       </c>
     </row>
     <row r="436">
@@ -5852,7 +5846,7 @@
         <v>16</v>
       </c>
       <c r="C441" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.329319610005894</v>
       </c>
     </row>
     <row r="442">
@@ -5885,7 +5879,7 @@
         <v>16</v>
       </c>
       <c r="C444" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.327876726247856</v>
       </c>
     </row>
     <row r="445">
@@ -5896,7 +5890,7 @@
         <v>16</v>
       </c>
       <c r="C445" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.294342681962847</v>
       </c>
     </row>
     <row r="446">
@@ -5907,7 +5901,7 @@
         <v>16</v>
       </c>
       <c r="C446" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.16813498020578</v>
       </c>
     </row>
     <row r="447">
@@ -5918,7 +5912,7 @@
         <v>16</v>
       </c>
       <c r="C447" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.597091149930633</v>
       </c>
     </row>
     <row r="448">
@@ -5940,7 +5934,7 @@
         <v>16</v>
       </c>
       <c r="C449" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.728003191104853</v>
       </c>
     </row>
     <row r="450">
@@ -5962,7 +5956,7 @@
         <v>16</v>
       </c>
       <c r="C451" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.28364196145445</v>
       </c>
     </row>
     <row r="452">
@@ -5973,7 +5967,7 @@
         <v>16</v>
       </c>
       <c r="C452" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.337331915314287</v>
       </c>
     </row>
     <row r="453">
@@ -5984,7 +5978,7 @@
         <v>16</v>
       </c>
       <c r="C453" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.2743204094098</v>
       </c>
     </row>
     <row r="454">
@@ -6006,7 +6000,7 @@
         <v>16</v>
       </c>
       <c r="C455" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.395056009431367</v>
       </c>
     </row>
     <row r="456">
@@ -6039,7 +6033,7 @@
         <v>16</v>
       </c>
       <c r="C458" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.226996827564834</v>
       </c>
     </row>
     <row r="459">
@@ -6072,7 +6066,7 @@
         <v>16</v>
       </c>
       <c r="C461" t="n">
-        <v>-0.154025227795202</v>
+        <v>-0.151778542893534</v>
       </c>
     </row>
     <row r="462">
@@ -6105,7 +6099,7 @@
         <v>16</v>
       </c>
       <c r="C464" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.532176219922255</v>
       </c>
     </row>
     <row r="465">
@@ -6116,7 +6110,7 @@
         <v>16</v>
       </c>
       <c r="C465" t="n">
-        <v>-0.171390867599079</v>
+        <v>-0.652020151583505</v>
       </c>
     </row>
     <row r="466">
@@ -6127,7 +6121,7 @@
         <v>16</v>
       </c>
       <c r="C466" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.429946492026818</v>
       </c>
     </row>
     <row r="467">
@@ -6138,7 +6132,7 @@
         <v>16</v>
       </c>
       <c r="C467" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.379290567836121</v>
       </c>
     </row>
     <row r="468">
@@ -6149,7 +6143,7 @@
         <v>16</v>
       </c>
       <c r="C468" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.378579711455163</v>
       </c>
     </row>
     <row r="469">
@@ -6193,7 +6187,7 @@
         <v>16</v>
       </c>
       <c r="C472" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.250873683585965</v>
       </c>
     </row>
     <row r="473">
@@ -6259,7 +6253,7 @@
         <v>16</v>
       </c>
       <c r="C478" t="n">
-        <v>-0.162838252399249</v>
+        <v>-0.225924148692394</v>
       </c>
     </row>
     <row r="479">
@@ -6270,7 +6264,7 @@
         <v>16</v>
       </c>
       <c r="C479" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.195787242522381</v>
       </c>
     </row>
     <row r="480">
@@ -6292,7 +6286,7 @@
         <v>16</v>
       </c>
       <c r="C481" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.185433428954554</v>
       </c>
     </row>
     <row r="482">
@@ -6325,7 +6319,7 @@
         <v>16</v>
       </c>
       <c r="C484" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.208813711477077</v>
       </c>
     </row>
     <row r="485">
@@ -6369,7 +6363,7 @@
         <v>16</v>
       </c>
       <c r="C488" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.245167834698343</v>
       </c>
     </row>
     <row r="489">
@@ -6380,7 +6374,7 @@
         <v>16</v>
       </c>
       <c r="C489" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.15708678868316</v>
       </c>
     </row>
     <row r="490">
@@ -6435,7 +6429,7 @@
         <v>16</v>
       </c>
       <c r="C494" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.306391225851887</v>
       </c>
     </row>
     <row r="495">
@@ -6446,7 +6440,7 @@
         <v>16</v>
       </c>
       <c r="C495" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.187588694644035</v>
       </c>
     </row>
     <row r="496">
@@ -6468,7 +6462,7 @@
         <v>16</v>
       </c>
       <c r="C497" t="n">
-        <v>-0.163279961841354</v>
+        <v>-0.134316144460987</v>
       </c>
     </row>
     <row r="498">
@@ -6479,7 +6473,7 @@
         <v>16</v>
       </c>
       <c r="C498" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.490400302332724</v>
       </c>
     </row>
     <row r="499">
@@ -6490,7 +6484,7 @@
         <v>16</v>
       </c>
       <c r="C499" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.215599028918832</v>
       </c>
     </row>
     <row r="500">
@@ -6534,7 +6528,7 @@
         <v>16</v>
       </c>
       <c r="C503" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.647601721958717</v>
       </c>
     </row>
     <row r="504">
@@ -6567,7 +6561,7 @@
         <v>16</v>
       </c>
       <c r="C506" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.193097775551729</v>
       </c>
     </row>
     <row r="507">
@@ -6578,7 +6572,7 @@
         <v>16</v>
       </c>
       <c r="C507" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.210953958549259</v>
       </c>
     </row>
     <row r="508">
@@ -6589,7 +6583,7 @@
         <v>16</v>
       </c>
       <c r="C508" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.202073324661181</v>
       </c>
     </row>
     <row r="509">
@@ -6611,7 +6605,7 @@
         <v>16</v>
       </c>
       <c r="C510" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.306146503466742</v>
       </c>
     </row>
     <row r="511">
@@ -6633,7 +6627,7 @@
         <v>16</v>
       </c>
       <c r="C512" t="n">
-        <v>-0.163224838446713</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="513">
@@ -6644,7 +6638,7 @@
         <v>16</v>
       </c>
       <c r="C513" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.238546427251966</v>
       </c>
     </row>
     <row r="514">
@@ -6655,7 +6649,7 @@
         <v>16</v>
       </c>
       <c r="C514" t="n">
-        <v>-0.16701930008597</v>
+        <v>-0.190769934673569</v>
       </c>
     </row>
     <row r="515">
@@ -6666,7 +6660,7 @@
         <v>16</v>
       </c>
       <c r="C515" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.472491199273305</v>
       </c>
     </row>
     <row r="516">
@@ -6688,7 +6682,7 @@
         <v>16</v>
       </c>
       <c r="C517" t="n">
-        <v>-0.160917485803499</v>
+        <v>-0.239919350058407</v>
       </c>
     </row>
     <row r="518">
@@ -6699,7 +6693,7 @@
         <v>16</v>
       </c>
       <c r="C518" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.170079193488258</v>
       </c>
     </row>
     <row r="519">
@@ -6721,7 +6715,7 @@
         <v>16</v>
       </c>
       <c r="C520" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.209883160691108</v>
       </c>
     </row>
     <row r="521">
@@ -6743,7 +6737,7 @@
         <v>16</v>
       </c>
       <c r="C522" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.38662526441124</v>
       </c>
     </row>
     <row r="523">
@@ -6754,7 +6748,7 @@
         <v>16</v>
       </c>
       <c r="C523" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.251397182388237</v>
       </c>
     </row>
     <row r="524">
@@ -6765,7 +6759,7 @@
         <v>16</v>
       </c>
       <c r="C524" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.15922481079698</v>
       </c>
     </row>
     <row r="525">
@@ -6776,7 +6770,7 @@
         <v>16</v>
       </c>
       <c r="C525" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.186942375255745</v>
       </c>
     </row>
     <row r="526">
@@ -6809,7 +6803,7 @@
         <v>16</v>
       </c>
       <c r="C528" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.347650862496449</v>
       </c>
     </row>
     <row r="529">
@@ -6831,7 +6825,7 @@
         <v>16</v>
       </c>
       <c r="C530" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.234103510488635</v>
       </c>
     </row>
     <row r="531">
@@ -6875,7 +6869,7 @@
         <v>16</v>
       </c>
       <c r="C534" t="n">
-        <v>-0.160529596081688</v>
+        <v>-0.14444695882443</v>
       </c>
     </row>
     <row r="535">
@@ -6897,7 +6891,7 @@
         <v>16</v>
       </c>
       <c r="C536" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.938730026401944</v>
       </c>
     </row>
     <row r="537">
@@ -6908,7 +6902,7 @@
         <v>16</v>
       </c>
       <c r="C537" t="n">
-        <v>-0.159763313609467</v>
+        <v>0.732192631910124</v>
       </c>
     </row>
     <row r="538">
@@ -7018,7 +7012,7 @@
         <v>16</v>
       </c>
       <c r="C547" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.46940233181213</v>
       </c>
     </row>
     <row r="548">
@@ -7029,7 +7023,7 @@
         <v>16</v>
       </c>
       <c r="C548" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.232541491365004</v>
       </c>
     </row>
     <row r="549">
@@ -7040,7 +7034,7 @@
         <v>16</v>
       </c>
       <c r="C549" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.0456307177524085</v>
       </c>
     </row>
     <row r="550">
@@ -7051,7 +7045,7 @@
         <v>16</v>
       </c>
       <c r="C550" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.292552484887352</v>
       </c>
     </row>
     <row r="551">
@@ -7073,7 +7067,7 @@
         <v>16</v>
       </c>
       <c r="C552" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.809578084611404</v>
       </c>
     </row>
     <row r="553">
@@ -7084,7 +7078,7 @@
         <v>16</v>
       </c>
       <c r="C553" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.145484157815953</v>
       </c>
     </row>
     <row r="554">
@@ -7106,7 +7100,7 @@
         <v>16</v>
       </c>
       <c r="C555" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.183120993594738</v>
       </c>
     </row>
     <row r="556">
@@ -7117,7 +7111,7 @@
         <v>16</v>
       </c>
       <c r="C556" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.904143583341</v>
       </c>
     </row>
     <row r="557">
@@ -7128,7 +7122,7 @@
         <v>16</v>
       </c>
       <c r="C557" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.538874654193771</v>
       </c>
     </row>
     <row r="558">
@@ -7139,7 +7133,7 @@
         <v>16</v>
       </c>
       <c r="C558" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.185247237666097</v>
       </c>
     </row>
     <row r="559">
@@ -7172,7 +7166,7 @@
         <v>16</v>
       </c>
       <c r="C561" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.387886683041353</v>
       </c>
     </row>
     <row r="562">
@@ -7183,7 +7177,7 @@
         <v>16</v>
       </c>
       <c r="C562" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.310170720613093</v>
       </c>
     </row>
     <row r="563">
@@ -7216,7 +7210,7 @@
         <v>16</v>
       </c>
       <c r="C565" t="n">
-        <v>-0.156560788634788</v>
+        <v>-0.129147726960616</v>
       </c>
     </row>
     <row r="566">
@@ -7227,7 +7221,7 @@
         <v>16</v>
       </c>
       <c r="C566" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.147779702623029</v>
       </c>
     </row>
     <row r="567">
@@ -7293,7 +7287,7 @@
         <v>16</v>
       </c>
       <c r="C572" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.167756304400811</v>
       </c>
     </row>
     <row r="573">
@@ -7304,7 +7298,7 @@
         <v>16</v>
       </c>
       <c r="C573" t="n">
-        <v>-0.157358462669212</v>
+        <v>-0.248650034029654</v>
       </c>
     </row>
     <row r="574">
@@ -7326,7 +7320,7 @@
         <v>16</v>
       </c>
       <c r="C575" t="n">
-        <v>-0.0739051790588059</v>
+        <v>0.725342422546754</v>
       </c>
     </row>
     <row r="576">
@@ -7337,7 +7331,7 @@
         <v>16</v>
       </c>
       <c r="C576" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.151673423403079</v>
       </c>
     </row>
     <row r="577">
@@ -7348,7 +7342,7 @@
         <v>16</v>
       </c>
       <c r="C577" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.319429261145628</v>
       </c>
     </row>
     <row r="578">
@@ -7370,7 +7364,7 @@
         <v>16</v>
       </c>
       <c r="C579" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.540652415907815</v>
       </c>
     </row>
     <row r="580">
@@ -7381,7 +7375,7 @@
         <v>16</v>
       </c>
       <c r="C580" t="n">
-        <v>-0.160495995618337</v>
+        <v>-0.24714020521583</v>
       </c>
     </row>
     <row r="581">
@@ -7392,7 +7386,7 @@
         <v>16</v>
       </c>
       <c r="C581" t="n">
-        <v>-0.16068772114112</v>
+        <v>-0.316164612526767</v>
       </c>
     </row>
     <row r="582">
@@ -7403,7 +7397,7 @@
         <v>16</v>
       </c>
       <c r="C582" t="n">
-        <v>-0.160616930149552</v>
+        <v>-0.512679887802836</v>
       </c>
     </row>
     <row r="583">
@@ -7436,7 +7430,7 @@
         <v>16</v>
       </c>
       <c r="C585" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.0663731733112423</v>
       </c>
     </row>
     <row r="586">
@@ -7447,7 +7441,7 @@
         <v>16</v>
       </c>
       <c r="C586" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.1814542861834</v>
       </c>
     </row>
     <row r="587">
@@ -7469,7 +7463,7 @@
         <v>16</v>
       </c>
       <c r="C588" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.264741463207891</v>
       </c>
     </row>
     <row r="589">
@@ -7480,7 +7474,7 @@
         <v>16</v>
       </c>
       <c r="C589" t="n">
-        <v>-0.157977701097999</v>
+        <v>-0.0118617303541404</v>
       </c>
     </row>
     <row r="590">
@@ -7502,7 +7496,7 @@
         <v>16</v>
       </c>
       <c r="C591" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.197822585768119</v>
       </c>
     </row>
     <row r="592">
@@ -7513,7 +7507,7 @@
         <v>16</v>
       </c>
       <c r="C592" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.166990562955692</v>
       </c>
     </row>
     <row r="593">
@@ -7535,7 +7529,7 @@
         <v>16</v>
       </c>
       <c r="C594" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.233000953944741</v>
       </c>
     </row>
     <row r="595">
@@ -7546,7 +7540,7 @@
         <v>16</v>
       </c>
       <c r="C595" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.194098526575372</v>
       </c>
     </row>
     <row r="596">
@@ -7579,7 +7573,7 @@
         <v>16</v>
       </c>
       <c r="C598" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.41791855056496</v>
       </c>
     </row>
     <row r="599">
@@ -7601,7 +7595,7 @@
         <v>16</v>
       </c>
       <c r="C600" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.155871342544056</v>
       </c>
     </row>
     <row r="601">
@@ -7689,7 +7683,7 @@
         <v>16</v>
       </c>
       <c r="C608" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.523846358345508</v>
       </c>
     </row>
     <row r="609">
@@ -7711,7 +7705,7 @@
         <v>16</v>
       </c>
       <c r="C610" t="n">
-        <v>-0.175193603641177</v>
+        <v>-0.362416298085077</v>
       </c>
     </row>
     <row r="611">
@@ -7722,7 +7716,7 @@
         <v>16</v>
       </c>
       <c r="C611" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.739089398435674</v>
       </c>
     </row>
     <row r="612">
@@ -7744,7 +7738,7 @@
         <v>16</v>
       </c>
       <c r="C613" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.272524704764565</v>
       </c>
     </row>
     <row r="614">
@@ -7865,7 +7859,7 @@
         <v>16</v>
       </c>
       <c r="C624" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.325165386374663</v>
       </c>
     </row>
     <row r="625">
@@ -7898,7 +7892,7 @@
         <v>16</v>
       </c>
       <c r="C627" t="n">
-        <v>-0.171953729017166</v>
+        <v>-0.121758688605007</v>
       </c>
     </row>
     <row r="628">
@@ -7953,7 +7947,7 @@
         <v>16</v>
       </c>
       <c r="C632" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.169337077344146</v>
       </c>
     </row>
     <row r="633">
@@ -8019,7 +8013,7 @@
         <v>16</v>
       </c>
       <c r="C638" t="n">
-        <v>-0.159763313609467</v>
+        <v>0.0298579415556276</v>
       </c>
     </row>
     <row r="639">
@@ -8030,7 +8024,7 @@
         <v>16</v>
       </c>
       <c r="C639" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.495450209505573</v>
       </c>
     </row>
     <row r="640">
@@ -8085,7 +8079,7 @@
         <v>16</v>
       </c>
       <c r="C644" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.229263174278053</v>
       </c>
     </row>
     <row r="645">
@@ -8096,7 +8090,7 @@
         <v>16</v>
       </c>
       <c r="C645" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.66820325491184</v>
       </c>
     </row>
     <row r="646">
@@ -8118,7 +8112,7 @@
         <v>16</v>
       </c>
       <c r="C647" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.200688106761533</v>
       </c>
     </row>
     <row r="648">
@@ -8129,7 +8123,7 @@
         <v>16</v>
       </c>
       <c r="C648" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.308470201068473</v>
       </c>
     </row>
     <row r="649">
@@ -8140,7 +8134,7 @@
         <v>16</v>
       </c>
       <c r="C649" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.345417403888454</v>
       </c>
     </row>
     <row r="650">
@@ -8162,7 +8156,7 @@
         <v>16</v>
       </c>
       <c r="C651" t="n">
-        <v>-0.159763313609467</v>
+        <v>0.100893387807956</v>
       </c>
     </row>
     <row r="652">
@@ -8173,7 +8167,7 @@
         <v>16</v>
       </c>
       <c r="C652" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.312634750200381</v>
       </c>
     </row>
     <row r="653">
@@ -8184,7 +8178,7 @@
         <v>16</v>
       </c>
       <c r="C653" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.230450450992817</v>
       </c>
     </row>
     <row r="654">
@@ -8239,7 +8233,7 @@
         <v>16</v>
       </c>
       <c r="C658" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.370225897617826</v>
       </c>
     </row>
     <row r="659">
@@ -8272,7 +8266,7 @@
         <v>16</v>
       </c>
       <c r="C661" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.169601809310494</v>
       </c>
     </row>
     <row r="662">
@@ -8283,7 +8277,7 @@
         <v>16</v>
       </c>
       <c r="C662" t="n">
-        <v>-0.159763313609467</v>
+        <v>0.292481584155682</v>
       </c>
     </row>
     <row r="663">
@@ -8305,7 +8299,7 @@
         <v>16</v>
       </c>
       <c r="C664" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.170034058633729</v>
       </c>
     </row>
     <row r="665">
@@ -8316,7 +8310,7 @@
         <v>16</v>
       </c>
       <c r="C665" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.219283399267056</v>
       </c>
     </row>
     <row r="666">
@@ -8327,7 +8321,7 @@
         <v>16</v>
       </c>
       <c r="C666" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.221033414108191</v>
       </c>
     </row>
     <row r="667">
@@ -8371,7 +8365,7 @@
         <v>16</v>
       </c>
       <c r="C670" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.13231451932824</v>
       </c>
     </row>
     <row r="671">
@@ -8382,7 +8376,7 @@
         <v>16</v>
       </c>
       <c r="C671" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.336074328915988</v>
       </c>
     </row>
     <row r="672">
@@ -8393,7 +8387,7 @@
         <v>16</v>
       </c>
       <c r="C672" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.481130576274606</v>
       </c>
     </row>
     <row r="673">
@@ -8415,7 +8409,7 @@
         <v>16</v>
       </c>
       <c r="C674" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.436128545693244</v>
       </c>
     </row>
     <row r="675">
@@ -8426,7 +8420,7 @@
         <v>16</v>
       </c>
       <c r="C675" t="n">
-        <v>-0.159354838636258</v>
+        <v>-0.168488505527136</v>
       </c>
     </row>
     <row r="676">
@@ -8448,7 +8442,7 @@
         <v>16</v>
       </c>
       <c r="C677" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.182671620459327</v>
       </c>
     </row>
     <row r="678">
@@ -8459,7 +8453,7 @@
         <v>16</v>
       </c>
       <c r="C678" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.564914847443405</v>
       </c>
     </row>
     <row r="679">
@@ -8514,7 +8508,7 @@
         <v>16</v>
       </c>
       <c r="C683" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.157149479167134</v>
       </c>
     </row>
     <row r="684">
@@ -8525,7 +8519,7 @@
         <v>16</v>
       </c>
       <c r="C684" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.79214797546326</v>
       </c>
     </row>
     <row r="685">
@@ -8591,7 +8585,7 @@
         <v>16</v>
       </c>
       <c r="C690" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.124456140745751</v>
       </c>
     </row>
     <row r="691">
@@ -8602,7 +8596,7 @@
         <v>16</v>
       </c>
       <c r="C691" t="n">
-        <v>-0.162228453932511</v>
+        <v>-0.163911402028968</v>
       </c>
     </row>
     <row r="692">
@@ -8635,7 +8629,7 @@
         <v>16</v>
       </c>
       <c r="C694" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.345774258781884</v>
       </c>
     </row>
     <row r="695">
@@ -8657,7 +8651,7 @@
         <v>16</v>
       </c>
       <c r="C696" t="n">
-        <v>-0.159763313609467</v>
+        <v>0.798406737715142</v>
       </c>
     </row>
     <row r="697">
@@ -8690,7 +8684,7 @@
         <v>16</v>
       </c>
       <c r="C699" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.314918559186587</v>
       </c>
     </row>
     <row r="700">
@@ -8789,7 +8783,7 @@
         <v>16</v>
       </c>
       <c r="C708" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.48092797749681</v>
       </c>
     </row>
     <row r="709">
@@ -8844,7 +8838,7 @@
         <v>16</v>
       </c>
       <c r="C713" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.283260205521106</v>
       </c>
     </row>
     <row r="714">
@@ -8877,7 +8871,7 @@
         <v>16</v>
       </c>
       <c r="C716" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.951674002835615</v>
       </c>
     </row>
     <row r="717">
@@ -8888,7 +8882,7 @@
         <v>16</v>
       </c>
       <c r="C717" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.259346124338428</v>
       </c>
     </row>
     <row r="718">
@@ -8899,7 +8893,7 @@
         <v>16</v>
       </c>
       <c r="C718" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.198128045887863</v>
       </c>
     </row>
     <row r="719">
@@ -8910,7 +8904,7 @@
         <v>16</v>
       </c>
       <c r="C719" t="n">
-        <v>-0.163855175559003</v>
+        <v>-0.192530260679875</v>
       </c>
     </row>
     <row r="720">
@@ -8921,7 +8915,7 @@
         <v>16</v>
       </c>
       <c r="C720" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.25483106970934</v>
       </c>
     </row>
     <row r="721">
@@ -8954,7 +8948,7 @@
         <v>16</v>
       </c>
       <c r="C723" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.167915800835773</v>
       </c>
     </row>
     <row r="724">
@@ -8976,7 +8970,7 @@
         <v>16</v>
       </c>
       <c r="C725" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.597486518944987</v>
       </c>
     </row>
     <row r="726">
@@ -9020,7 +9014,7 @@
         <v>16</v>
       </c>
       <c r="C729" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.0561920661760915</v>
       </c>
     </row>
     <row r="730">
@@ -9031,7 +9025,7 @@
         <v>16</v>
       </c>
       <c r="C730" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.224682951967972</v>
       </c>
     </row>
     <row r="731">
@@ -9042,7 +9036,7 @@
         <v>16</v>
       </c>
       <c r="C731" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.16054210403446</v>
       </c>
     </row>
     <row r="732">
@@ -9064,7 +9058,7 @@
         <v>16</v>
       </c>
       <c r="C733" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.1600994755179</v>
       </c>
     </row>
     <row r="734">
@@ -9075,7 +9069,7 @@
         <v>16</v>
       </c>
       <c r="C734" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.156794682155091</v>
       </c>
     </row>
     <row r="735">
@@ -9097,7 +9091,7 @@
         <v>16</v>
       </c>
       <c r="C736" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.247061334317785</v>
       </c>
     </row>
     <row r="737">
@@ -9141,7 +9135,7 @@
         <v>16</v>
       </c>
       <c r="C740" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.235690555670192</v>
       </c>
     </row>
     <row r="741">
@@ -9152,7 +9146,7 @@
         <v>16</v>
       </c>
       <c r="C741" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.262043490741146</v>
       </c>
     </row>
     <row r="742">
@@ -9207,7 +9201,7 @@
         <v>16</v>
       </c>
       <c r="C746" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.350781206274824</v>
       </c>
     </row>
     <row r="747">
@@ -9262,7 +9256,7 @@
         <v>16</v>
       </c>
       <c r="C751" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.185848730555039</v>
       </c>
     </row>
     <row r="752">
@@ -9273,7 +9267,7 @@
         <v>16</v>
       </c>
       <c r="C752" t="n">
-        <v>-0.144167563512512</v>
+        <v>-0.0110402189421008</v>
       </c>
     </row>
     <row r="753">
@@ -9284,7 +9278,7 @@
         <v>16</v>
       </c>
       <c r="C753" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.395432994895877</v>
       </c>
     </row>
     <row r="754">
@@ -9317,7 +9311,7 @@
         <v>16</v>
       </c>
       <c r="C756" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.226224364517573</v>
       </c>
     </row>
     <row r="757">
@@ -9361,7 +9355,7 @@
         <v>16</v>
       </c>
       <c r="C760" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.175826428380318</v>
       </c>
     </row>
     <row r="761">
@@ -9416,7 +9410,7 @@
         <v>16</v>
       </c>
       <c r="C765" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.217913883771242</v>
       </c>
     </row>
     <row r="766">
@@ -9460,7 +9454,7 @@
         <v>16</v>
       </c>
       <c r="C769" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.362396645466992</v>
       </c>
     </row>
     <row r="770">
@@ -9471,7 +9465,7 @@
         <v>16</v>
       </c>
       <c r="C770" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.208927790913064</v>
       </c>
     </row>
     <row r="771">
@@ -9482,7 +9476,7 @@
         <v>16</v>
       </c>
       <c r="C771" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.332918750207375</v>
       </c>
     </row>
     <row r="772">
@@ -9493,7 +9487,7 @@
         <v>16</v>
       </c>
       <c r="C772" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.108405398268563</v>
       </c>
     </row>
     <row r="773">
@@ -9504,7 +9498,7 @@
         <v>16</v>
       </c>
       <c r="C773" t="n">
-        <v>-0.159763313609467</v>
+        <v>0.342977996021057</v>
       </c>
     </row>
     <row r="774">
@@ -9526,7 +9520,7 @@
         <v>16</v>
       </c>
       <c r="C775" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.164610475480455</v>
       </c>
     </row>
     <row r="776">
@@ -9548,7 +9542,7 @@
         <v>16</v>
       </c>
       <c r="C777" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.174392511751245</v>
       </c>
     </row>
     <row r="778">
@@ -9603,7 +9597,7 @@
         <v>16</v>
       </c>
       <c r="C782" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.602093505869734</v>
       </c>
     </row>
     <row r="783">
@@ -9625,7 +9619,7 @@
         <v>16</v>
       </c>
       <c r="C784" t="n">
-        <v>-0.170411410571299</v>
+        <v>-0.352667196242493</v>
       </c>
     </row>
     <row r="785">
@@ -9636,7 +9630,7 @@
         <v>16</v>
       </c>
       <c r="C785" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.215694439403493</v>
       </c>
     </row>
     <row r="786">
@@ -9647,7 +9641,7 @@
         <v>16</v>
       </c>
       <c r="C786" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.162703439650948</v>
       </c>
     </row>
     <row r="787">
@@ -9669,7 +9663,7 @@
         <v>16</v>
       </c>
       <c r="C788" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.888676520803846</v>
       </c>
     </row>
     <row r="789">
@@ -9680,7 +9674,7 @@
         <v>16</v>
       </c>
       <c r="C789" t="n">
-        <v>-0.159763313609468</v>
+        <v>0.0761413787996846</v>
       </c>
     </row>
     <row r="790">
@@ -9691,7 +9685,7 @@
         <v>16</v>
       </c>
       <c r="C790" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.0714008576878322</v>
       </c>
     </row>
     <row r="791">
@@ -9713,7 +9707,7 @@
         <v>16</v>
       </c>
       <c r="C792" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.230311485566562</v>
       </c>
     </row>
     <row r="793">
@@ -9757,7 +9751,7 @@
         <v>16</v>
       </c>
       <c r="C796" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.146429736438694</v>
       </c>
     </row>
     <row r="797">
@@ -9779,7 +9773,7 @@
         <v>16</v>
       </c>
       <c r="C798" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.211972873847429</v>
       </c>
     </row>
     <row r="799">
@@ -9801,7 +9795,7 @@
         <v>16</v>
       </c>
       <c r="C800" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.330260559314035</v>
       </c>
     </row>
     <row r="801">
@@ -9823,7 +9817,7 @@
         <v>16</v>
       </c>
       <c r="C802" t="n">
-        <v>-0.17802194814483</v>
+        <v>-0.285521679499335</v>
       </c>
     </row>
     <row r="803">
@@ -9834,7 +9828,7 @@
         <v>16</v>
       </c>
       <c r="C803" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.194139327213351</v>
       </c>
     </row>
     <row r="804">
@@ -9845,7 +9839,7 @@
         <v>16</v>
       </c>
       <c r="C804" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.609364295622115</v>
       </c>
     </row>
     <row r="805">
@@ -9856,7 +9850,7 @@
         <v>16</v>
       </c>
       <c r="C805" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.579386567929633</v>
       </c>
     </row>
     <row r="806">
@@ -9889,7 +9883,7 @@
         <v>16</v>
       </c>
       <c r="C808" t="n">
-        <v>-0.16586717686007</v>
+        <v>0.371332576961072</v>
       </c>
     </row>
     <row r="809">
@@ -9944,7 +9938,7 @@
         <v>16</v>
       </c>
       <c r="C813" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.19076096740823</v>
       </c>
     </row>
     <row r="814">
@@ -9955,7 +9949,7 @@
         <v>16</v>
       </c>
       <c r="C814" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.403734513841045</v>
       </c>
     </row>
     <row r="815">
@@ -9966,7 +9960,7 @@
         <v>16</v>
       </c>
       <c r="C815" t="n">
-        <v>-0.166328388763804</v>
+        <v>-0.184865171787109</v>
       </c>
     </row>
     <row r="816">
@@ -9977,7 +9971,7 @@
         <v>16</v>
       </c>
       <c r="C816" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.258245097028542</v>
       </c>
     </row>
     <row r="817">
@@ -9999,7 +9993,7 @@
         <v>16</v>
       </c>
       <c r="C818" t="n">
-        <v>-0.142534561420849</v>
+        <v>0.399172111723965</v>
       </c>
     </row>
     <row r="819">
@@ -10032,7 +10026,7 @@
         <v>16</v>
       </c>
       <c r="C821" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.227294538827558</v>
       </c>
     </row>
     <row r="822">
@@ -10054,7 +10048,7 @@
         <v>16</v>
       </c>
       <c r="C823" t="n">
-        <v>-0.202801206640454</v>
+        <v>-0.603355473301131</v>
       </c>
     </row>
     <row r="824">
@@ -10065,7 +10059,7 @@
         <v>16</v>
       </c>
       <c r="C824" t="n">
-        <v>-0.162069811766084</v>
+        <v>-0.186756406628353</v>
       </c>
     </row>
     <row r="825">
@@ -10076,7 +10070,7 @@
         <v>16</v>
       </c>
       <c r="C825" t="n">
-        <v>-0.186150200823207</v>
+        <v>-0.282967362708751</v>
       </c>
     </row>
     <row r="826">
@@ -10109,7 +10103,7 @@
         <v>16</v>
       </c>
       <c r="C828" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.165087393011044</v>
       </c>
     </row>
     <row r="829">
@@ -10120,7 +10114,7 @@
         <v>16</v>
       </c>
       <c r="C829" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.176371475003678</v>
       </c>
     </row>
     <row r="830">
@@ -10186,7 +10180,7 @@
         <v>16</v>
       </c>
       <c r="C835" t="n">
-        <v>-0.0320896034929721</v>
+        <v>0.069526082281335</v>
       </c>
     </row>
     <row r="836">
@@ -10197,7 +10191,7 @@
         <v>16</v>
       </c>
       <c r="C836" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.259847347210616</v>
       </c>
     </row>
     <row r="837">
@@ -10252,7 +10246,7 @@
         <v>16</v>
       </c>
       <c r="C841" t="n">
-        <v>-0.200487950868209</v>
+        <v>-0.699385863378558</v>
       </c>
     </row>
     <row r="842">
@@ -10263,7 +10257,7 @@
         <v>16</v>
       </c>
       <c r="C842" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.161372486781536</v>
       </c>
     </row>
     <row r="843">
@@ -10274,7 +10268,7 @@
         <v>16</v>
       </c>
       <c r="C843" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.229373325506487</v>
       </c>
     </row>
     <row r="844">
@@ -10285,7 +10279,7 @@
         <v>16</v>
       </c>
       <c r="C844" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.179579391687858</v>
       </c>
     </row>
     <row r="845">
@@ -10296,7 +10290,7 @@
         <v>16</v>
       </c>
       <c r="C845" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.489481810621216</v>
       </c>
     </row>
     <row r="846">
@@ -10318,7 +10312,7 @@
         <v>16</v>
       </c>
       <c r="C847" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.185186958383608</v>
       </c>
     </row>
     <row r="848">
@@ -10340,7 +10334,7 @@
         <v>16</v>
       </c>
       <c r="C849" t="n">
-        <v>-0.204131036172131</v>
+        <v>0.347825004972526</v>
       </c>
     </row>
     <row r="850">
@@ -10351,7 +10345,7 @@
         <v>16</v>
       </c>
       <c r="C850" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.166787173999096</v>
       </c>
     </row>
     <row r="851">
@@ -10395,7 +10389,7 @@
         <v>16</v>
       </c>
       <c r="C854" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.200498610779596</v>
       </c>
     </row>
     <row r="855">
@@ -10406,7 +10400,7 @@
         <v>16</v>
       </c>
       <c r="C855" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.0637829708325006</v>
       </c>
     </row>
     <row r="856">
@@ -10417,7 +10411,7 @@
         <v>16</v>
       </c>
       <c r="C856" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.557589284761111</v>
       </c>
     </row>
     <row r="857">
@@ -10439,7 +10433,7 @@
         <v>16</v>
       </c>
       <c r="C858" t="n">
-        <v>-0.0997758302341969</v>
+        <v>0.648420314517249</v>
       </c>
     </row>
     <row r="859">
@@ -10450,7 +10444,7 @@
         <v>16</v>
       </c>
       <c r="C859" t="n">
-        <v>-0.16016229107533</v>
+        <v>-0.17568478584899</v>
       </c>
     </row>
     <row r="860">
@@ -10461,7 +10455,7 @@
         <v>16</v>
       </c>
       <c r="C860" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.276040110105038</v>
       </c>
     </row>
     <row r="861">
@@ -10494,7 +10488,7 @@
         <v>16</v>
       </c>
       <c r="C863" t="n">
-        <v>-0.159763313609468</v>
+        <v>-2.21981367806201</v>
       </c>
     </row>
     <row r="864">
@@ -10505,7 +10499,7 @@
         <v>16</v>
       </c>
       <c r="C864" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.225974591132093</v>
       </c>
     </row>
     <row r="865">
@@ -10527,7 +10521,7 @@
         <v>16</v>
       </c>
       <c r="C866" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.216471784846369</v>
       </c>
     </row>
     <row r="867">
@@ -10538,7 +10532,7 @@
         <v>16</v>
       </c>
       <c r="C867" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.178033156559359</v>
       </c>
     </row>
     <row r="868">
@@ -10549,7 +10543,7 @@
         <v>16</v>
       </c>
       <c r="C868" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.310219204490068</v>
       </c>
     </row>
     <row r="869">
@@ -10582,7 +10576,7 @@
         <v>16</v>
       </c>
       <c r="C871" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.197326128641592</v>
       </c>
     </row>
     <row r="872">
@@ -10604,7 +10598,7 @@
         <v>16</v>
       </c>
       <c r="C873" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.229784254341748</v>
       </c>
     </row>
     <row r="874">
@@ -10615,7 +10609,7 @@
         <v>16</v>
       </c>
       <c r="C874" t="n">
-        <v>-0.168904288168263</v>
+        <v>-0.100663596464663</v>
       </c>
     </row>
     <row r="875">
@@ -10637,7 +10631,7 @@
         <v>16</v>
       </c>
       <c r="C876" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.669497284864151</v>
       </c>
     </row>
     <row r="877">
@@ -10659,7 +10653,7 @@
         <v>16</v>
       </c>
       <c r="C878" t="n">
-        <v>-0.161556385420605</v>
+        <v>0.0508131126812118</v>
       </c>
     </row>
     <row r="879">
@@ -10670,7 +10664,7 @@
         <v>16</v>
       </c>
       <c r="C879" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.253386266482655</v>
       </c>
     </row>
     <row r="880">
@@ -10692,7 +10686,7 @@
         <v>16</v>
       </c>
       <c r="C881" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.465272189456257</v>
       </c>
     </row>
     <row r="882">
@@ -10703,7 +10697,7 @@
         <v>16</v>
       </c>
       <c r="C882" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.183352260112656</v>
       </c>
     </row>
     <row r="883">
@@ -10714,7 +10708,7 @@
         <v>16</v>
       </c>
       <c r="C883" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.263789269957557</v>
       </c>
     </row>
     <row r="884">
@@ -10725,7 +10719,7 @@
         <v>16</v>
       </c>
       <c r="C884" t="n">
-        <v>-0.184997197628748</v>
+        <v>-0.200400705298255</v>
       </c>
     </row>
     <row r="885">
@@ -10736,7 +10730,7 @@
         <v>16</v>
       </c>
       <c r="C885" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.323291822236767</v>
       </c>
     </row>
     <row r="886">
@@ -10791,7 +10785,7 @@
         <v>16</v>
       </c>
       <c r="C890" t="n">
-        <v>-0.18478240131707</v>
+        <v>-0.671603346056758</v>
       </c>
     </row>
     <row r="891">
@@ -10813,7 +10807,7 @@
         <v>16</v>
       </c>
       <c r="C892" t="n">
-        <v>-0.162802340186613</v>
+        <v>-0.150397183047742</v>
       </c>
     </row>
     <row r="893">
@@ -10824,7 +10818,7 @@
         <v>16</v>
       </c>
       <c r="C893" t="n">
-        <v>-0.158135089827579</v>
+        <v>-0.0890946990060115</v>
       </c>
     </row>
     <row r="894">
@@ -10890,7 +10884,7 @@
         <v>16</v>
       </c>
       <c r="C899" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.593904494817344</v>
       </c>
     </row>
     <row r="900">
@@ -10912,7 +10906,7 @@
         <v>16</v>
       </c>
       <c r="C901" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.169439164586781</v>
       </c>
     </row>
     <row r="902">
@@ -10967,7 +10961,7 @@
         <v>16</v>
       </c>
       <c r="C906" t="n">
-        <v>-0.16252770996685</v>
+        <v>-0.193053266132442</v>
       </c>
     </row>
     <row r="907">
@@ -10989,7 +10983,7 @@
         <v>16</v>
       </c>
       <c r="C908" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.268354435589091</v>
       </c>
     </row>
     <row r="909">
@@ -11000,7 +10994,7 @@
         <v>16</v>
       </c>
       <c r="C909" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.612697806761539</v>
       </c>
     </row>
     <row r="910">
@@ -11011,7 +11005,7 @@
         <v>16</v>
       </c>
       <c r="C910" t="n">
-        <v>-0.161951284269477</v>
+        <v>-0.200726288365184</v>
       </c>
     </row>
     <row r="911">
@@ -11033,7 +11027,7 @@
         <v>16</v>
       </c>
       <c r="C912" t="n">
-        <v>-0.16233249335963</v>
+        <v>-0.160452325445993</v>
       </c>
     </row>
     <row r="913">
@@ -11044,7 +11038,7 @@
         <v>16</v>
       </c>
       <c r="C913" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.146083326514573</v>
       </c>
     </row>
     <row r="914">
@@ -11066,7 +11060,7 @@
         <v>16</v>
       </c>
       <c r="C915" t="n">
-        <v>-0.0814604174025106</v>
+        <v>0.581252604691528</v>
       </c>
     </row>
     <row r="916">
@@ -11077,7 +11071,7 @@
         <v>16</v>
       </c>
       <c r="C916" t="n">
-        <v>-0.200861693686408</v>
+        <v>-0.271691011755454</v>
       </c>
     </row>
     <row r="917">
@@ -11088,7 +11082,7 @@
         <v>16</v>
       </c>
       <c r="C917" t="n">
-        <v>-0.162361163534947</v>
+        <v>-0.270480757959303</v>
       </c>
     </row>
     <row r="918">
@@ -11121,7 +11115,7 @@
         <v>16</v>
       </c>
       <c r="C920" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.183753971084862</v>
       </c>
     </row>
     <row r="921">
@@ -11132,7 +11126,7 @@
         <v>16</v>
       </c>
       <c r="C921" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.163440287358176</v>
       </c>
     </row>
     <row r="922">
@@ -11143,7 +11137,7 @@
         <v>16</v>
       </c>
       <c r="C922" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.387918275567956</v>
       </c>
     </row>
     <row r="923">
@@ -11154,7 +11148,7 @@
         <v>16</v>
       </c>
       <c r="C923" t="n">
-        <v>-0.166239251340418</v>
+        <v>-0.175475591060902</v>
       </c>
     </row>
     <row r="924">
@@ -11176,7 +11170,7 @@
         <v>16</v>
       </c>
       <c r="C925" t="n">
-        <v>-0.160544910830433</v>
+        <v>-0.288556790846379</v>
       </c>
     </row>
     <row r="926">
@@ -11209,7 +11203,7 @@
         <v>16</v>
       </c>
       <c r="C928" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.179698716211391</v>
       </c>
     </row>
     <row r="929">
@@ -11231,7 +11225,7 @@
         <v>16</v>
       </c>
       <c r="C930" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.187816795120178</v>
       </c>
     </row>
     <row r="931">
@@ -11264,7 +11258,7 @@
         <v>16</v>
       </c>
       <c r="C933" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.194140910069097</v>
       </c>
     </row>
     <row r="934">
@@ -11275,7 +11269,7 @@
         <v>16</v>
       </c>
       <c r="C934" t="n">
-        <v>-0.172843284691174</v>
+        <v>-0.157174359372443</v>
       </c>
     </row>
     <row r="935">
@@ -11297,7 +11291,7 @@
         <v>16</v>
       </c>
       <c r="C936" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.509664128509363</v>
       </c>
     </row>
     <row r="937">
@@ -11308,7 +11302,7 @@
         <v>16</v>
       </c>
       <c r="C937" t="n">
-        <v>-0.179422852175872</v>
+        <v>-0.232355965507449</v>
       </c>
     </row>
     <row r="938">
@@ -11319,7 +11313,7 @@
         <v>16</v>
       </c>
       <c r="C938" t="n">
-        <v>-0.11085025819946</v>
+        <v>0.731038728391175</v>
       </c>
     </row>
     <row r="939">
@@ -11341,7 +11335,7 @@
         <v>16</v>
       </c>
       <c r="C940" t="n">
-        <v>-0.0291813401833265</v>
+        <v>0.12999221400947</v>
       </c>
     </row>
     <row r="941">
@@ -11352,7 +11346,7 @@
         <v>16</v>
       </c>
       <c r="C941" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.364708021812008</v>
       </c>
     </row>
     <row r="942">
@@ -11363,7 +11357,7 @@
         <v>16</v>
       </c>
       <c r="C942" t="n">
-        <v>-0.164672145830739</v>
+        <v>-0.16802954991554</v>
       </c>
     </row>
     <row r="943">
@@ -11374,7 +11368,7 @@
         <v>16</v>
       </c>
       <c r="C943" t="n">
-        <v>-0.16410731338906</v>
+        <v>-0.17630514706605</v>
       </c>
     </row>
     <row r="944">
@@ -11396,7 +11390,7 @@
         <v>16</v>
       </c>
       <c r="C945" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.569816637497971</v>
       </c>
     </row>
     <row r="946">
@@ -11429,7 +11423,7 @@
         <v>16</v>
       </c>
       <c r="C948" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.480637584216346</v>
       </c>
     </row>
     <row r="949">
@@ -11473,7 +11467,7 @@
         <v>16</v>
       </c>
       <c r="C952" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.479331017490904</v>
       </c>
     </row>
     <row r="953">
@@ -11484,7 +11478,7 @@
         <v>16</v>
       </c>
       <c r="C953" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.73378154145979</v>
       </c>
     </row>
     <row r="954">
@@ -11495,7 +11489,7 @@
         <v>16</v>
       </c>
       <c r="C954" t="n">
-        <v>-0.161252514410771</v>
+        <v>-0.189151106569905</v>
       </c>
     </row>
     <row r="955">
@@ -11506,7 +11500,7 @@
         <v>16</v>
       </c>
       <c r="C955" t="n">
-        <v>-0.174088183765486</v>
+        <v>-0.200600738234151</v>
       </c>
     </row>
     <row r="956">
@@ -11528,7 +11522,7 @@
         <v>16</v>
       </c>
       <c r="C957" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.215280613990703</v>
       </c>
     </row>
     <row r="958">
@@ -11550,7 +11544,7 @@
         <v>16</v>
       </c>
       <c r="C959" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.218285441297166</v>
       </c>
     </row>
     <row r="960">
@@ -11561,7 +11555,7 @@
         <v>16</v>
       </c>
       <c r="C960" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.626655467139383</v>
       </c>
     </row>
     <row r="961">
@@ -11594,7 +11588,7 @@
         <v>16</v>
       </c>
       <c r="C963" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.291621980623926</v>
       </c>
     </row>
     <row r="964">
@@ -11638,7 +11632,7 @@
         <v>16</v>
       </c>
       <c r="C967" t="n">
-        <v>-0.164302488488915</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="968">
@@ -11660,7 +11654,7 @@
         <v>16</v>
       </c>
       <c r="C969" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.209095795630086</v>
       </c>
     </row>
     <row r="970">
@@ -11693,7 +11687,7 @@
         <v>16</v>
       </c>
       <c r="C972" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.523305224471769</v>
       </c>
     </row>
     <row r="973">
@@ -11704,7 +11698,7 @@
         <v>16</v>
       </c>
       <c r="C973" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.233776717982028</v>
       </c>
     </row>
     <row r="974">
@@ -11715,7 +11709,7 @@
         <v>16</v>
       </c>
       <c r="C974" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.919971780591085</v>
       </c>
     </row>
     <row r="975">
@@ -11726,7 +11720,7 @@
         <v>16</v>
       </c>
       <c r="C975" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.215312273655557</v>
       </c>
     </row>
     <row r="976">
@@ -11737,7 +11731,7 @@
         <v>16</v>
       </c>
       <c r="C976" t="n">
-        <v>-0.165390081581795</v>
+        <v>-0.186665174567088</v>
       </c>
     </row>
     <row r="977">
@@ -11759,7 +11753,7 @@
         <v>16</v>
       </c>
       <c r="C978" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.313792348165782</v>
       </c>
     </row>
     <row r="979">
@@ -11770,7 +11764,7 @@
         <v>16</v>
       </c>
       <c r="C979" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.137423637981339</v>
       </c>
     </row>
     <row r="980">
@@ -11803,7 +11797,7 @@
         <v>16</v>
       </c>
       <c r="C982" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.177475611039325</v>
       </c>
     </row>
     <row r="983">
@@ -11814,7 +11808,7 @@
         <v>16</v>
       </c>
       <c r="C983" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.298425732587668</v>
       </c>
     </row>
     <row r="984">
@@ -11836,7 +11830,7 @@
         <v>16</v>
       </c>
       <c r="C985" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.255973731100499</v>
       </c>
     </row>
     <row r="986">
@@ -11847,7 +11841,7 @@
         <v>16</v>
       </c>
       <c r="C986" t="n">
-        <v>-0.206381898029838</v>
+        <v>-0.198966373302015</v>
       </c>
     </row>
     <row r="987">
@@ -11869,7 +11863,7 @@
         <v>16</v>
       </c>
       <c r="C988" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.165065556697339</v>
       </c>
     </row>
     <row r="989">
@@ -11891,7 +11885,7 @@
         <v>16</v>
       </c>
       <c r="C990" t="n">
-        <v>-0.160409988397176</v>
+        <v>-0.262736445581276</v>
       </c>
     </row>
     <row r="991">
@@ -11902,7 +11896,7 @@
         <v>16</v>
       </c>
       <c r="C991" t="n">
-        <v>-0.160880736054883</v>
+        <v>-0.182205630926757</v>
       </c>
     </row>
     <row r="992">
@@ -11913,7 +11907,7 @@
         <v>16</v>
       </c>
       <c r="C992" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.59454705600638</v>
       </c>
     </row>
     <row r="993">
@@ -11957,7 +11951,7 @@
         <v>16</v>
       </c>
       <c r="C996" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.168477364792962</v>
       </c>
     </row>
     <row r="997">
@@ -11968,7 +11962,7 @@
         <v>16</v>
       </c>
       <c r="C997" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.160854483381818</v>
       </c>
     </row>
     <row r="998">
@@ -11979,7 +11973,7 @@
         <v>16</v>
       </c>
       <c r="C998" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.281038930759643</v>
       </c>
     </row>
     <row r="999">
@@ -12001,7 +11995,7 @@
         <v>16</v>
       </c>
       <c r="C1000" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.163257652842491</v>
       </c>
     </row>
     <row r="1001">
@@ -12045,7 +12039,7 @@
         <v>16</v>
       </c>
       <c r="C1004" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.301418041193774</v>
       </c>
     </row>
     <row r="1005">
@@ -12067,7 +12061,7 @@
         <v>16</v>
       </c>
       <c r="C1006" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.215959491869524</v>
       </c>
     </row>
     <row r="1007">
@@ -12078,7 +12072,7 @@
         <v>16</v>
       </c>
       <c r="C1007" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.214967978260878</v>
       </c>
     </row>
     <row r="1008">
@@ -12100,7 +12094,7 @@
         <v>16</v>
       </c>
       <c r="C1009" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.268708332799569</v>
       </c>
     </row>
     <row r="1010">
@@ -12111,7 +12105,7 @@
         <v>16</v>
       </c>
       <c r="C1010" t="n">
-        <v>-0.173611111111111</v>
+        <v>-1.39371962135035</v>
       </c>
     </row>
     <row r="1011">
@@ -12155,7 +12149,7 @@
         <v>16</v>
       </c>
       <c r="C1014" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.452434568939992</v>
       </c>
     </row>
     <row r="1015">
@@ -12177,7 +12171,7 @@
         <v>16</v>
       </c>
       <c r="C1016" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.62444001128636</v>
       </c>
     </row>
     <row r="1017">
@@ -12188,7 +12182,7 @@
         <v>16</v>
       </c>
       <c r="C1017" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.764428489336784</v>
       </c>
     </row>
     <row r="1018">
@@ -12199,7 +12193,7 @@
         <v>16</v>
       </c>
       <c r="C1018" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.218255646849363</v>
       </c>
     </row>
     <row r="1019">
@@ -12210,7 +12204,7 @@
         <v>16</v>
       </c>
       <c r="C1019" t="n">
-        <v>-0.171912283833134</v>
+        <v>0.485876178691636</v>
       </c>
     </row>
     <row r="1020">
@@ -12243,7 +12237,7 @@
         <v>16</v>
       </c>
       <c r="C1022" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.17255289506516</v>
       </c>
     </row>
     <row r="1023">
@@ -12254,7 +12248,7 @@
         <v>16</v>
       </c>
       <c r="C1023" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.170499430438007</v>
       </c>
     </row>
     <row r="1024">
@@ -12265,7 +12259,7 @@
         <v>16</v>
       </c>
       <c r="C1024" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.526224108419295</v>
       </c>
     </row>
     <row r="1025">
@@ -12309,7 +12303,7 @@
         <v>16</v>
       </c>
       <c r="C1028" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.534243924895703</v>
       </c>
     </row>
     <row r="1029">
@@ -12353,7 +12347,7 @@
         <v>16</v>
       </c>
       <c r="C1032" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.191970678874274</v>
       </c>
     </row>
     <row r="1033">
@@ -12375,7 +12369,7 @@
         <v>16</v>
       </c>
       <c r="C1034" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.529655731401877</v>
       </c>
     </row>
     <row r="1035">
@@ -12386,7 +12380,7 @@
         <v>16</v>
       </c>
       <c r="C1035" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.301507777829728</v>
       </c>
     </row>
     <row r="1036">
@@ -12408,7 +12402,7 @@
         <v>16</v>
       </c>
       <c r="C1037" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.433662258739496</v>
       </c>
     </row>
     <row r="1038">
@@ -12430,7 +12424,7 @@
         <v>16</v>
       </c>
       <c r="C1039" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.188613695312828</v>
       </c>
     </row>
     <row r="1040">
@@ -12485,7 +12479,7 @@
         <v>16</v>
       </c>
       <c r="C1044" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.127693090635828</v>
       </c>
     </row>
     <row r="1045">
@@ -12496,7 +12490,7 @@
         <v>16</v>
       </c>
       <c r="C1045" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.342565503248003</v>
       </c>
     </row>
     <row r="1046">
@@ -12507,7 +12501,7 @@
         <v>16</v>
       </c>
       <c r="C1046" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.29590465920362</v>
       </c>
     </row>
     <row r="1047">
@@ -12518,7 +12512,7 @@
         <v>16</v>
       </c>
       <c r="C1047" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.316039149683722</v>
       </c>
     </row>
     <row r="1048">
@@ -12540,7 +12534,7 @@
         <v>16</v>
       </c>
       <c r="C1049" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.460542235038731</v>
       </c>
     </row>
     <row r="1050">
@@ -12584,7 +12578,7 @@
         <v>16</v>
       </c>
       <c r="C1053" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.355841138388012</v>
       </c>
     </row>
     <row r="1054">
@@ -12606,7 +12600,7 @@
         <v>16</v>
       </c>
       <c r="C1055" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.190509517019481</v>
       </c>
     </row>
     <row r="1056">
@@ -12617,7 +12611,7 @@
         <v>16</v>
       </c>
       <c r="C1056" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.192642608372185</v>
       </c>
     </row>
     <row r="1057">
@@ -12639,7 +12633,7 @@
         <v>16</v>
       </c>
       <c r="C1058" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.185575967193226</v>
       </c>
     </row>
     <row r="1059">
@@ -12661,7 +12655,7 @@
         <v>16</v>
       </c>
       <c r="C1060" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.246313564722579</v>
       </c>
     </row>
     <row r="1061">
@@ -12683,7 +12677,7 @@
         <v>16</v>
       </c>
       <c r="C1062" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.19687986457572</v>
       </c>
     </row>
     <row r="1063">
@@ -12694,7 +12688,7 @@
         <v>16</v>
       </c>
       <c r="C1063" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.1488873644173</v>
       </c>
     </row>
     <row r="1064">
@@ -12716,7 +12710,7 @@
         <v>16</v>
       </c>
       <c r="C1065" t="n">
-        <v>-0.194550100452022</v>
+        <v>-0.348389437584008</v>
       </c>
     </row>
     <row r="1066">
@@ -12727,7 +12721,7 @@
         <v>16</v>
       </c>
       <c r="C1066" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.374971455609459</v>
       </c>
     </row>
     <row r="1067">
@@ -12793,7 +12787,7 @@
         <v>16</v>
       </c>
       <c r="C1072" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.189973684324531</v>
       </c>
     </row>
     <row r="1073">
@@ -12804,7 +12798,7 @@
         <v>16</v>
       </c>
       <c r="C1073" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.207440677855633</v>
       </c>
     </row>
     <row r="1074">
@@ -12815,7 +12809,7 @@
         <v>16</v>
       </c>
       <c r="C1074" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.526393472874731</v>
       </c>
     </row>
     <row r="1075">
@@ -12859,7 +12853,7 @@
         <v>16</v>
       </c>
       <c r="C1078" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.131520193181248</v>
       </c>
     </row>
     <row r="1079">
@@ -12870,7 +12864,7 @@
         <v>16</v>
       </c>
       <c r="C1079" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.141516743273565</v>
       </c>
     </row>
     <row r="1080">
@@ -12881,7 +12875,7 @@
         <v>16</v>
       </c>
       <c r="C1080" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.219446363075228</v>
       </c>
     </row>
     <row r="1081">
@@ -12892,7 +12886,7 @@
         <v>16</v>
       </c>
       <c r="C1081" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.449865814998196</v>
       </c>
     </row>
     <row r="1082">
@@ -12914,7 +12908,7 @@
         <v>16</v>
       </c>
       <c r="C1083" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.221188047263249</v>
       </c>
     </row>
     <row r="1084">
@@ -12925,7 +12919,7 @@
         <v>16</v>
       </c>
       <c r="C1084" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.354807507576842</v>
       </c>
     </row>
     <row r="1085">
@@ -12969,7 +12963,7 @@
         <v>16</v>
       </c>
       <c r="C1088" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.350286907056067</v>
       </c>
     </row>
     <row r="1089">
@@ -13002,7 +12996,7 @@
         <v>16</v>
       </c>
       <c r="C1091" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.341555904935823</v>
       </c>
     </row>
     <row r="1092">
@@ -13013,7 +13007,7 @@
         <v>16</v>
       </c>
       <c r="C1092" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.18186327733923</v>
       </c>
     </row>
     <row r="1093">
@@ -13035,7 +13029,7 @@
         <v>16</v>
       </c>
       <c r="C1094" t="n">
-        <v>-0.187901106216898</v>
+        <v>-0.542893021795806</v>
       </c>
     </row>
     <row r="1095">
@@ -13068,7 +13062,7 @@
         <v>16</v>
       </c>
       <c r="C1097" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.346833482747707</v>
       </c>
     </row>
     <row r="1098">
@@ -13079,7 +13073,7 @@
         <v>16</v>
       </c>
       <c r="C1098" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.182657856556612</v>
       </c>
     </row>
     <row r="1099">
@@ -13112,7 +13106,7 @@
         <v>16</v>
       </c>
       <c r="C1101" t="n">
-        <v>-0.166744413316893</v>
+        <v>0.127581796168353</v>
       </c>
     </row>
     <row r="1102">
@@ -13145,7 +13139,7 @@
         <v>16</v>
       </c>
       <c r="C1104" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.470209770222578</v>
       </c>
     </row>
     <row r="1105">
@@ -13178,7 +13172,7 @@
         <v>16</v>
       </c>
       <c r="C1107" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.201060302834202</v>
       </c>
     </row>
     <row r="1108">
@@ -13211,7 +13205,7 @@
         <v>16</v>
       </c>
       <c r="C1110" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.226063058544729</v>
       </c>
     </row>
     <row r="1111">
@@ -13222,7 +13216,7 @@
         <v>16</v>
       </c>
       <c r="C1111" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.139504076638432</v>
       </c>
     </row>
     <row r="1112">
@@ -13255,7 +13249,7 @@
         <v>16</v>
       </c>
       <c r="C1114" t="n">
-        <v>-0.054545445456867</v>
+        <v>0.290935298686129</v>
       </c>
     </row>
     <row r="1115">
@@ -13277,7 +13271,7 @@
         <v>16</v>
       </c>
       <c r="C1116" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.1042684291014</v>
       </c>
     </row>
     <row r="1117">
@@ -13288,7 +13282,7 @@
         <v>16</v>
       </c>
       <c r="C1117" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.193348711077179</v>
       </c>
     </row>
     <row r="1118">
@@ -13299,7 +13293,7 @@
         <v>16</v>
       </c>
       <c r="C1118" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.418275286032156</v>
       </c>
     </row>
     <row r="1119">
@@ -13332,7 +13326,7 @@
         <v>16</v>
       </c>
       <c r="C1121" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.879973152998303</v>
       </c>
     </row>
     <row r="1122">
@@ -13343,7 +13337,7 @@
         <v>16</v>
       </c>
       <c r="C1122" t="n">
-        <v>-0.173611111111111</v>
+        <v>0.179184754839587</v>
       </c>
     </row>
     <row r="1123">
@@ -13365,7 +13359,7 @@
         <v>16</v>
       </c>
       <c r="C1124" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.22186797265821</v>
       </c>
     </row>
     <row r="1125">
@@ -13387,7 +13381,7 @@
         <v>16</v>
       </c>
       <c r="C1126" t="n">
-        <v>-0.173611111111111</v>
+        <v>-1.56025906591077</v>
       </c>
     </row>
     <row r="1127">
@@ -13398,7 +13392,7 @@
         <v>16</v>
       </c>
       <c r="C1127" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.317501266023297</v>
       </c>
     </row>
     <row r="1128">
@@ -13409,7 +13403,7 @@
         <v>16</v>
       </c>
       <c r="C1128" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.210195284712803</v>
       </c>
     </row>
     <row r="1129">
@@ -13442,7 +13436,7 @@
         <v>16</v>
       </c>
       <c r="C1131" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.182208305979153</v>
       </c>
     </row>
     <row r="1132">
@@ -13464,7 +13458,7 @@
         <v>16</v>
       </c>
       <c r="C1133" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.232678999135556</v>
       </c>
     </row>
     <row r="1134">
@@ -13486,7 +13480,7 @@
         <v>16</v>
       </c>
       <c r="C1135" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.257303029429499</v>
       </c>
     </row>
     <row r="1136">
@@ -13497,7 +13491,7 @@
         <v>16</v>
       </c>
       <c r="C1136" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.18313663301415</v>
       </c>
     </row>
     <row r="1137">
@@ -13519,7 +13513,7 @@
         <v>16</v>
       </c>
       <c r="C1138" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.316618916115718</v>
       </c>
     </row>
     <row r="1139">
@@ -13541,7 +13535,7 @@
         <v>16</v>
       </c>
       <c r="C1140" t="n">
-        <v>-0.177083523300043</v>
+        <v>-0.298967646725327</v>
       </c>
     </row>
     <row r="1141">
@@ -13552,7 +13546,7 @@
         <v>16</v>
       </c>
       <c r="C1141" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.189170060981689</v>
       </c>
     </row>
     <row r="1142">
@@ -13563,7 +13557,7 @@
         <v>16</v>
       </c>
       <c r="C1142" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.250539972935685</v>
       </c>
     </row>
     <row r="1143">
@@ -13585,7 +13579,7 @@
         <v>16</v>
       </c>
       <c r="C1144" t="n">
-        <v>-0.202796745418731</v>
+        <v>-0.345438396405558</v>
       </c>
     </row>
     <row r="1145">
@@ -13662,7 +13656,7 @@
         <v>16</v>
       </c>
       <c r="C1151" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.295153864836965</v>
       </c>
     </row>
     <row r="1152">
@@ -13684,7 +13678,7 @@
         <v>16</v>
       </c>
       <c r="C1153" t="n">
-        <v>-0.17803227402529</v>
+        <v>-0.133046161624939</v>
       </c>
     </row>
     <row r="1154">
@@ -13739,7 +13733,7 @@
         <v>16</v>
       </c>
       <c r="C1158" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.285523278026751</v>
       </c>
     </row>
     <row r="1159">
@@ -13750,7 +13744,7 @@
         <v>16</v>
       </c>
       <c r="C1159" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.257736814070864</v>
       </c>
     </row>
     <row r="1160">
@@ -13761,7 +13755,7 @@
         <v>16</v>
       </c>
       <c r="C1160" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.216967798907464</v>
       </c>
     </row>
     <row r="1161">
@@ -13772,7 +13766,7 @@
         <v>16</v>
       </c>
       <c r="C1161" t="n">
-        <v>-0.173611111111111</v>
+        <v>0.072693793583358</v>
       </c>
     </row>
     <row r="1162">
@@ -13805,7 +13799,7 @@
         <v>16</v>
       </c>
       <c r="C1164" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.451597208642668</v>
       </c>
     </row>
     <row r="1165">
@@ -13860,7 +13854,7 @@
         <v>16</v>
       </c>
       <c r="C1169" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.183403414209879</v>
       </c>
     </row>
     <row r="1170">
@@ -13871,7 +13865,7 @@
         <v>16</v>
       </c>
       <c r="C1170" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.189747688080373</v>
       </c>
     </row>
     <row r="1171">
@@ -13904,7 +13898,7 @@
         <v>16</v>
       </c>
       <c r="C1173" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.0753567792629495</v>
       </c>
     </row>
     <row r="1174">
@@ -13915,7 +13909,7 @@
         <v>16</v>
       </c>
       <c r="C1174" t="n">
-        <v>-0.100696048965821</v>
+        <v>-0.0312702419279161</v>
       </c>
     </row>
     <row r="1175">
@@ -14047,7 +14041,7 @@
         <v>16</v>
       </c>
       <c r="C1186" t="n">
-        <v>-0.177964638936772</v>
+        <v>-0.138446153966465</v>
       </c>
     </row>
     <row r="1187">
@@ -14058,7 +14052,7 @@
         <v>16</v>
       </c>
       <c r="C1187" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.539079103264526</v>
       </c>
     </row>
     <row r="1188">
@@ -14113,7 +14107,7 @@
         <v>16</v>
       </c>
       <c r="C1192" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.690021905926403</v>
       </c>
     </row>
     <row r="1193">
@@ -14124,7 +14118,7 @@
         <v>16</v>
       </c>
       <c r="C1193" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.283973661395231</v>
       </c>
     </row>
     <row r="1194">
@@ -14146,7 +14140,7 @@
         <v>16</v>
       </c>
       <c r="C1195" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.408214201438836</v>
       </c>
     </row>
     <row r="1196">
@@ -14157,7 +14151,7 @@
         <v>16</v>
       </c>
       <c r="C1196" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.38598898378008</v>
       </c>
     </row>
     <row r="1197">
@@ -14168,7 +14162,7 @@
         <v>16</v>
       </c>
       <c r="C1197" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.392133392203696</v>
       </c>
     </row>
     <row r="1198">
@@ -14179,7 +14173,7 @@
         <v>16</v>
       </c>
       <c r="C1198" t="n">
-        <v>-0.173611111111111</v>
+        <v>-1.00535100629217</v>
       </c>
     </row>
     <row r="1199">
@@ -14190,7 +14184,7 @@
         <v>16</v>
       </c>
       <c r="C1199" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.476326717847786</v>
       </c>
     </row>
     <row r="1200">
@@ -14201,7 +14195,7 @@
         <v>16</v>
       </c>
       <c r="C1200" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.476303024053466</v>
       </c>
     </row>
     <row r="1201">
@@ -14937,7 +14931,7 @@
         <v>-1491.94</v>
       </c>
       <c r="E42" t="n">
-        <v>150.104615384615</v>
+        <v>1793.99974295035</v>
       </c>
     </row>
     <row r="43">
@@ -15413,7 +15407,7 @@
         <v>5</v>
       </c>
       <c r="E70" t="n">
-        <v>45.3846153846154</v>
+        <v>101.501529762842</v>
       </c>
     </row>
     <row r="71">
@@ -15447,7 +15441,7 @@
         <v>5</v>
       </c>
       <c r="E72" t="n">
-        <v>9.25</v>
+        <v>-2.13656795648836</v>
       </c>
     </row>
     <row r="73">
@@ -15583,7 +15577,7 @@
         <v>6</v>
       </c>
       <c r="E80" t="n">
-        <v>9.16666666666667</v>
+        <v>10.5562701485874</v>
       </c>
     </row>
     <row r="81">
@@ -15651,7 +15645,7 @@
         <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>9.58333333333333</v>
+        <v>8.61780887374477</v>
       </c>
     </row>
   </sheetData>
@@ -15871,13 +15865,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D13" t="n">
         <v>14</v>
@@ -15888,13 +15882,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
         <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
         <v>14</v>
@@ -15911,7 +15905,7 @@
         <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>14</v>
@@ -15928,7 +15922,7 @@
         <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
         <v>14</v>
@@ -15945,7 +15939,7 @@
         <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D17" t="n">
         <v>14</v>
@@ -15962,7 +15956,7 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -15979,7 +15973,7 @@
         <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D19" t="n">
         <v>14</v>
@@ -15996,7 +15990,7 @@
         <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D20" t="n">
         <v>14</v>
@@ -16013,7 +16007,7 @@
         <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D21" t="n">
         <v>14</v>
@@ -16030,7 +16024,7 @@
         <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D22" t="n">
         <v>14</v>
@@ -16047,7 +16041,7 @@
         <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D23" t="n">
         <v>14</v>
@@ -16058,13 +16052,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B24" t="s">
         <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D24" t="n">
         <v>14</v>
@@ -16075,13 +16069,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B25" t="s">
         <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D25" t="n">
         <v>14</v>
@@ -16092,13 +16086,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B26" t="s">
         <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D26" t="n">
         <v>14</v>
@@ -16109,13 +16103,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B27" t="s">
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D27" t="n">
         <v>14</v>
@@ -16132,7 +16126,7 @@
         <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D28" t="n">
         <v>14</v>
@@ -16149,7 +16143,7 @@
         <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D29" t="n">
         <v>14</v>
@@ -16166,7 +16160,7 @@
         <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D30" t="n">
         <v>14</v>
@@ -16183,7 +16177,7 @@
         <v>16</v>
       </c>
       <c r="C31" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D31" t="n">
         <v>14</v>
@@ -16200,7 +16194,7 @@
         <v>16</v>
       </c>
       <c r="C32" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D32" t="n">
         <v>14</v>
@@ -16217,7 +16211,7 @@
         <v>16</v>
       </c>
       <c r="C33" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D33" t="n">
         <v>14</v>
@@ -16234,7 +16228,7 @@
         <v>16</v>
       </c>
       <c r="C34" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D34" t="n">
         <v>14</v>
@@ -16245,13 +16239,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B35" t="s">
         <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D35" t="n">
         <v>14</v>
@@ -16262,13 +16256,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B36" t="s">
         <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D36" t="n">
         <v>14</v>
@@ -16279,13 +16273,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B37" t="s">
         <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D37" t="n">
         <v>14</v>
@@ -16296,13 +16290,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B38" t="s">
         <v>16</v>
       </c>
       <c r="C38" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D38" t="n">
         <v>14</v>
@@ -16313,13 +16307,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B39" t="s">
         <v>16</v>
       </c>
       <c r="C39" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D39" t="n">
         <v>14</v>
@@ -16330,13 +16324,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B40" t="s">
         <v>16</v>
       </c>
       <c r="C40" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D40" t="n">
         <v>14</v>
@@ -16353,7 +16347,7 @@
         <v>16</v>
       </c>
       <c r="C41" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D41" t="n">
         <v>14</v>
@@ -16370,7 +16364,7 @@
         <v>16</v>
       </c>
       <c r="C42" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D42" t="n">
         <v>14</v>
@@ -16387,7 +16381,7 @@
         <v>16</v>
       </c>
       <c r="C43" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D43" t="n">
         <v>14</v>
@@ -16404,7 +16398,7 @@
         <v>16</v>
       </c>
       <c r="C44" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D44" t="n">
         <v>14</v>
@@ -16421,7 +16415,7 @@
         <v>16</v>
       </c>
       <c r="C45" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D45" t="n">
         <v>14</v>
@@ -16432,13 +16426,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B46" t="s">
         <v>16</v>
       </c>
       <c r="C46" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D46" t="n">
         <v>14</v>
@@ -16449,13 +16443,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B47" t="s">
         <v>16</v>
       </c>
       <c r="C47" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D47" t="n">
         <v>14</v>
@@ -16466,13 +16460,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B48" t="s">
         <v>16</v>
       </c>
       <c r="C48" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D48" t="n">
         <v>14</v>
@@ -16483,13 +16477,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B49" t="s">
         <v>16</v>
       </c>
       <c r="C49" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D49" t="n">
         <v>14</v>
@@ -16500,13 +16494,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B50" t="s">
         <v>16</v>
       </c>
       <c r="C50" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D50" t="n">
         <v>14</v>
@@ -16517,13 +16511,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B51" t="s">
         <v>16</v>
       </c>
       <c r="C51" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D51" t="n">
         <v>14</v>
@@ -16534,13 +16528,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B52" t="s">
         <v>16</v>
       </c>
       <c r="C52" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D52" t="n">
         <v>14</v>
@@ -16551,13 +16545,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B53" t="s">
         <v>16</v>
       </c>
       <c r="C53" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D53" t="n">
         <v>14</v>
@@ -16574,7 +16568,7 @@
         <v>16</v>
       </c>
       <c r="C54" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D54" t="n">
         <v>14</v>
@@ -16591,7 +16585,7 @@
         <v>16</v>
       </c>
       <c r="C55" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D55" t="n">
         <v>14</v>
@@ -16608,7 +16602,7 @@
         <v>16</v>
       </c>
       <c r="C56" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D56" t="n">
         <v>14</v>
@@ -16619,16 +16613,16 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B57" t="s">
         <v>16</v>
       </c>
       <c r="C57" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D57" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E57" t="n">
         <v>1</v>
@@ -16636,16 +16630,16 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B58" t="s">
         <v>16</v>
       </c>
       <c r="C58" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D58" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E58" t="n">
         <v>1</v>
@@ -16653,16 +16647,16 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B59" t="s">
         <v>16</v>
       </c>
       <c r="C59" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D59" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E59" t="n">
         <v>1</v>
@@ -16670,16 +16664,16 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B60" t="s">
         <v>16</v>
       </c>
       <c r="C60" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E60" t="n">
         <v>1</v>
@@ -16687,16 +16681,16 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B61" t="s">
         <v>16</v>
       </c>
       <c r="C61" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D61" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E61" t="n">
         <v>1</v>
@@ -16704,16 +16698,16 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B62" t="s">
         <v>16</v>
       </c>
       <c r="C62" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D62" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E62" t="n">
         <v>1</v>
@@ -16721,16 +16715,16 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B63" t="s">
         <v>16</v>
       </c>
       <c r="C63" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D63" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E63" t="n">
         <v>1</v>
@@ -16738,16 +16732,16 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B64" t="s">
         <v>16</v>
       </c>
       <c r="C64" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D64" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E64" t="n">
         <v>1</v>
@@ -16755,16 +16749,16 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B65" t="s">
         <v>16</v>
       </c>
       <c r="C65" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D65" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E65" t="n">
         <v>1</v>
@@ -16772,16 +16766,16 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B66" t="s">
         <v>16</v>
       </c>
       <c r="C66" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D66" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
@@ -16795,216 +16789,12 @@
         <v>16</v>
       </c>
       <c r="C67" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D67" t="n">
         <v>13</v>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>21</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="s">
-        <v>43</v>
-      </c>
-      <c r="D68" t="n">
-        <v>13</v>
-      </c>
-      <c r="E68" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>21</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="s">
-        <v>44</v>
-      </c>
-      <c r="D69" t="n">
-        <v>13</v>
-      </c>
-      <c r="E69" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>21</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="s">
-        <v>45</v>
-      </c>
-      <c r="D70" t="n">
-        <v>13</v>
-      </c>
-      <c r="E70" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>21</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="s">
-        <v>46</v>
-      </c>
-      <c r="D71" t="n">
-        <v>13</v>
-      </c>
-      <c r="E71" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>21</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="s">
-        <v>47</v>
-      </c>
-      <c r="D72" t="n">
-        <v>13</v>
-      </c>
-      <c r="E72" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>21</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="s">
-        <v>48</v>
-      </c>
-      <c r="D73" t="n">
-        <v>13</v>
-      </c>
-      <c r="E73" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>21</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="s">
-        <v>49</v>
-      </c>
-      <c r="D74" t="n">
-        <v>13</v>
-      </c>
-      <c r="E74" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>21</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="s">
-        <v>50</v>
-      </c>
-      <c r="D75" t="n">
-        <v>13</v>
-      </c>
-      <c r="E75" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>21</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="s">
-        <v>51</v>
-      </c>
-      <c r="D76" t="n">
-        <v>13</v>
-      </c>
-      <c r="E76" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>21</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="s">
-        <v>52</v>
-      </c>
-      <c r="D77" t="n">
-        <v>13</v>
-      </c>
-      <c r="E77" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>21</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="s">
-        <v>53</v>
-      </c>
-      <c r="D78" t="n">
-        <v>13</v>
-      </c>
-      <c r="E78" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>21</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="s">
-        <v>54</v>
-      </c>
-      <c r="D79" t="n">
-        <v>13</v>
-      </c>
-      <c r="E79" t="n">
         <v>1</v>
       </c>
     </row>
